--- a/歌单.xlsx
+++ b/歌单.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3739" uniqueCount="1869">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3748" uniqueCount="1874">
   <si>
     <t>歌名</t>
   </si>
@@ -3371,6 +3371,9 @@
     <t>浪费</t>
   </si>
   <si>
+    <t>恋人</t>
+  </si>
+  <si>
     <t>莉莉安</t>
   </si>
   <si>
@@ -3749,6 +3752,12 @@
     <t>陈珊妮</t>
   </si>
   <si>
+    <t>牵手</t>
+  </si>
+  <si>
+    <t>苏芮</t>
+  </si>
+  <si>
     <t>牵丝戏</t>
   </si>
   <si>
@@ -5418,6 +5427,12 @@
   </si>
   <si>
     <t>Kiri T</t>
+  </si>
+  <si>
+    <t>用背脊唱情歌</t>
+  </si>
+  <si>
+    <t>Gareth.T</t>
   </si>
   <si>
     <t>13楼的大笨象</t>
@@ -6794,7 +6809,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F1199"/>
+  <dimension ref="A1:F1202"/>
   <sheetFormatPr defaultColWidth="35.625" defaultRowHeight="23.5" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="41.875" style="1" customWidth="1"/>
@@ -14434,29 +14449,29 @@
         <v>1113</v>
       </c>
       <c r="B637" s="2" t="s">
-        <v>1114</v>
-      </c>
-      <c r="C637" s="2" t="s">
-        <v>970</v>
+        <v>779</v>
+      </c>
+      <c r="C637" s="1" t="s">
+        <v>694</v>
       </c>
     </row>
     <row r="638" customHeight="1" spans="1:3">
       <c r="A638" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B638" s="2" t="s">
         <v>1115</v>
       </c>
-      <c r="B638" s="2" t="s">
-        <v>1116</v>
-      </c>
-      <c r="C638" s="1" t="s">
-        <v>694</v>
+      <c r="C638" s="2" t="s">
+        <v>970</v>
       </c>
     </row>
     <row r="639" customHeight="1" spans="1:3">
       <c r="A639" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B639" s="2" t="s">
         <v>1117</v>
-      </c>
-      <c r="B639" s="2" t="s">
-        <v>876</v>
       </c>
       <c r="C639" s="1" t="s">
         <v>694</v>
@@ -14467,7 +14482,7 @@
         <v>1118</v>
       </c>
       <c r="B640" s="2" t="s">
-        <v>1119</v>
+        <v>876</v>
       </c>
       <c r="C640" s="1" t="s">
         <v>694</v>
@@ -14475,13 +14490,13 @@
     </row>
     <row r="641" customHeight="1" spans="1:3">
       <c r="A641" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B641" s="2" t="s">
         <v>1120</v>
       </c>
-      <c r="B641" s="2" t="s">
-        <v>1026</v>
-      </c>
-      <c r="C641" s="2" t="s">
-        <v>762</v>
+      <c r="C641" s="1" t="s">
+        <v>694</v>
       </c>
     </row>
     <row r="642" customHeight="1" spans="1:3">
@@ -14489,10 +14504,10 @@
         <v>1121</v>
       </c>
       <c r="B642" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="C642" s="1" t="s">
-        <v>694</v>
+        <v>1026</v>
+      </c>
+      <c r="C642" s="2" t="s">
+        <v>762</v>
       </c>
     </row>
     <row r="643" customHeight="1" spans="1:3">
@@ -14500,21 +14515,21 @@
         <v>1122</v>
       </c>
       <c r="B643" s="2" t="s">
-        <v>1123</v>
-      </c>
-      <c r="C643" s="2" t="s">
-        <v>970</v>
+        <v>735</v>
+      </c>
+      <c r="C643" s="1" t="s">
+        <v>694</v>
       </c>
     </row>
     <row r="644" customHeight="1" spans="1:3">
       <c r="A644" s="2" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B644" s="2" t="s">
         <v>1124</v>
       </c>
-      <c r="B644" s="2" t="s">
-        <v>794</v>
-      </c>
-      <c r="C644" s="1" t="s">
-        <v>694</v>
+      <c r="C644" s="2" t="s">
+        <v>970</v>
       </c>
     </row>
     <row r="645" customHeight="1" spans="1:3">
@@ -14522,21 +14537,21 @@
         <v>1125</v>
       </c>
       <c r="B645" s="2" t="s">
-        <v>1126</v>
-      </c>
-      <c r="C645" s="2" t="s">
-        <v>970</v>
+        <v>794</v>
+      </c>
+      <c r="C645" s="1" t="s">
+        <v>694</v>
       </c>
     </row>
     <row r="646" customHeight="1" spans="1:3">
       <c r="A646" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B646" s="2" t="s">
         <v>1127</v>
       </c>
-      <c r="B646" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="C646" s="1" t="s">
-        <v>694</v>
+      <c r="C646" s="2" t="s">
+        <v>970</v>
       </c>
     </row>
     <row r="647" customHeight="1" spans="1:3">
@@ -14544,21 +14559,21 @@
         <v>1128</v>
       </c>
       <c r="B647" s="2" t="s">
-        <v>1129</v>
-      </c>
-      <c r="C647" s="2" t="s">
-        <v>762</v>
+        <v>1111</v>
+      </c>
+      <c r="C647" s="1" t="s">
+        <v>694</v>
       </c>
     </row>
     <row r="648" customHeight="1" spans="1:3">
       <c r="A648" s="2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B648" s="2" t="s">
         <v>1130</v>
       </c>
-      <c r="B648" s="2" t="s">
-        <v>747</v>
-      </c>
       <c r="C648" s="2" t="s">
-        <v>970</v>
+        <v>762</v>
       </c>
     </row>
     <row r="649" customHeight="1" spans="1:3">
@@ -14566,18 +14581,18 @@
         <v>1131</v>
       </c>
       <c r="B649" s="2" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C649" s="1" t="s">
-        <v>694</v>
+        <v>747</v>
+      </c>
+      <c r="C649" s="2" t="s">
+        <v>970</v>
       </c>
     </row>
     <row r="650" customHeight="1" spans="1:3">
       <c r="A650" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B650" s="2" t="s">
         <v>1133</v>
-      </c>
-      <c r="B650" s="2" t="s">
-        <v>766</v>
       </c>
       <c r="C650" s="1" t="s">
         <v>694</v>
@@ -14588,7 +14603,7 @@
         <v>1134</v>
       </c>
       <c r="B651" s="2" t="s">
-        <v>1135</v>
+        <v>766</v>
       </c>
       <c r="C651" s="1" t="s">
         <v>694</v>
@@ -14596,10 +14611,10 @@
     </row>
     <row r="652" customHeight="1" spans="1:3">
       <c r="A652" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B652" s="2" t="s">
         <v>1136</v>
-      </c>
-      <c r="B652" s="2" t="s">
-        <v>749</v>
       </c>
       <c r="C652" s="1" t="s">
         <v>694</v>
@@ -14610,21 +14625,21 @@
         <v>1137</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>1138</v>
-      </c>
-      <c r="C653" s="2" t="s">
-        <v>762</v>
+        <v>749</v>
+      </c>
+      <c r="C653" s="1" t="s">
+        <v>694</v>
       </c>
     </row>
     <row r="654" customHeight="1" spans="1:3">
       <c r="A654" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B654" s="2" t="s">
         <v>1139</v>
       </c>
-      <c r="B654" s="2" t="s">
-        <v>794</v>
-      </c>
-      <c r="C654" s="1" t="s">
-        <v>694</v>
+      <c r="C654" s="2" t="s">
+        <v>762</v>
       </c>
     </row>
     <row r="655" customHeight="1" spans="1:3">
@@ -14632,21 +14647,21 @@
         <v>1140</v>
       </c>
       <c r="B655" s="2" t="s">
-        <v>1141</v>
-      </c>
-      <c r="C655" s="2" t="s">
-        <v>970</v>
+        <v>794</v>
+      </c>
+      <c r="C655" s="1" t="s">
+        <v>694</v>
       </c>
     </row>
     <row r="656" customHeight="1" spans="1:3">
       <c r="A656" s="2" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B656" s="2" t="s">
         <v>1142</v>
       </c>
-      <c r="B656" s="2" t="s">
-        <v>794</v>
-      </c>
-      <c r="C656" s="1" t="s">
-        <v>694</v>
+      <c r="C656" s="2" t="s">
+        <v>970</v>
       </c>
     </row>
     <row r="657" customHeight="1" spans="1:4">
@@ -14654,7 +14669,7 @@
         <v>1143</v>
       </c>
       <c r="B657" s="2" t="s">
-        <v>1144</v>
+        <v>794</v>
       </c>
       <c r="C657" s="1" t="s">
         <v>694</v>
@@ -14662,12 +14677,12 @@
     </row>
     <row r="658" customHeight="1" spans="1:4">
       <c r="A658" s="2" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B658" s="2" t="s">
         <v>1145</v>
       </c>
-      <c r="B658" s="2" t="s">
-        <v>740</v>
-      </c>
-      <c r="C658" s="2" t="s">
+      <c r="C658" s="1" t="s">
         <v>694</v>
       </c>
     </row>
@@ -14676,9 +14691,9 @@
         <v>1146</v>
       </c>
       <c r="B659" s="2" t="s">
-        <v>804</v>
-      </c>
-      <c r="C659" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="C659" s="2" t="s">
         <v>694</v>
       </c>
     </row>
@@ -14687,7 +14702,7 @@
         <v>1147</v>
       </c>
       <c r="B660" s="2" t="s">
-        <v>1148</v>
+        <v>804</v>
       </c>
       <c r="C660" s="1" t="s">
         <v>694</v>
@@ -14695,10 +14710,10 @@
     </row>
     <row r="661" customHeight="1" spans="1:4">
       <c r="A661" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B661" s="2" t="s">
         <v>1149</v>
-      </c>
-      <c r="B661" s="2" t="s">
-        <v>766</v>
       </c>
       <c r="C661" s="1" t="s">
         <v>694</v>
@@ -14709,44 +14724,44 @@
         <v>1150</v>
       </c>
       <c r="B662" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="C662" s="1" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="663" customHeight="1" spans="1:4">
+      <c r="A663" s="2" t="s">
         <v>1151</v>
       </c>
-      <c r="C662" s="2" t="s">
+      <c r="B663" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C663" s="2" t="s">
         <v>762</v>
       </c>
     </row>
-    <row r="663" customHeight="1" spans="1:4">
-      <c r="A663" s="13" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B663" s="13" t="s">
+    <row r="664" customHeight="1" spans="1:4">
+      <c r="A664" s="13" t="s">
         <v>1153</v>
       </c>
-      <c r="C663" s="13" t="s">
+      <c r="B664" s="13" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C664" s="13" t="s">
         <v>702</v>
       </c>
-      <c r="D663" s="14"/>
-    </row>
-    <row r="664" customHeight="1" spans="1:4">
-      <c r="A664" s="2" t="s">
-        <v>1154</v>
-      </c>
-      <c r="B664" s="2" t="s">
-        <v>820</v>
-      </c>
-      <c r="C664" s="2" t="s">
-        <v>762</v>
-      </c>
+      <c r="D664" s="14"/>
     </row>
     <row r="665" customHeight="1" spans="1:4">
       <c r="A665" s="2" t="s">
         <v>1155</v>
       </c>
       <c r="B665" s="2" t="s">
-        <v>751</v>
-      </c>
-      <c r="C665" s="1" t="s">
-        <v>694</v>
+        <v>820</v>
+      </c>
+      <c r="C665" s="2" t="s">
+        <v>762</v>
       </c>
     </row>
     <row r="666" customHeight="1" spans="1:4">
@@ -14754,20 +14769,20 @@
         <v>1156</v>
       </c>
       <c r="B666" s="2" t="s">
-        <v>1157</v>
-      </c>
-      <c r="C666" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="C666" s="1" t="s">
         <v>694</v>
       </c>
     </row>
     <row r="667" customHeight="1" spans="1:4">
       <c r="A667" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B667" s="2" t="s">
         <v>1158</v>
       </c>
-      <c r="B667" s="2" t="s">
-        <v>740</v>
-      </c>
-      <c r="C667" s="1" t="s">
+      <c r="C667" s="2" t="s">
         <v>694</v>
       </c>
     </row>
@@ -14776,7 +14791,7 @@
         <v>1159</v>
       </c>
       <c r="B668" s="2" t="s">
-        <v>1160</v>
+        <v>740</v>
       </c>
       <c r="C668" s="1" t="s">
         <v>694</v>
@@ -14784,10 +14799,10 @@
     </row>
     <row r="669" customHeight="1" spans="1:4">
       <c r="A669" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B669" s="2" t="s">
         <v>1161</v>
-      </c>
-      <c r="B669" s="2" t="s">
-        <v>1162</v>
       </c>
       <c r="C669" s="1" t="s">
         <v>694</v>
@@ -14795,44 +14810,44 @@
     </row>
     <row r="670" customHeight="1" spans="1:4">
       <c r="A670" s="2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B670" s="2" t="s">
         <v>1163</v>
       </c>
-      <c r="B670" s="2" t="s">
+      <c r="C670" s="1" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="671" customHeight="1" spans="1:4">
+      <c r="A671" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B671" s="2" t="s">
         <v>964</v>
       </c>
-      <c r="C670" s="1" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="671" customHeight="1" spans="1:4">
-      <c r="A671" s="13" t="s">
-        <v>1164</v>
-      </c>
-      <c r="B671" s="13" t="s">
+      <c r="C671" s="1" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="672" customHeight="1" spans="1:4">
+      <c r="A672" s="13" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B672" s="13" t="s">
         <v>735</v>
       </c>
-      <c r="C671" s="13" t="s">
+      <c r="C672" s="13" t="s">
         <v>736</v>
       </c>
-      <c r="D671" s="14"/>
-    </row>
-    <row r="672" customHeight="1" spans="1:4">
-      <c r="A672" s="2" t="s">
-        <v>1165</v>
-      </c>
-      <c r="B672" s="2" t="s">
-        <v>693</v>
-      </c>
-      <c r="C672" s="1" t="s">
-        <v>694</v>
-      </c>
+      <c r="D672" s="14"/>
     </row>
     <row r="673" customHeight="1" spans="1:3">
       <c r="A673" s="2" t="s">
         <v>1166</v>
       </c>
       <c r="B673" s="2" t="s">
-        <v>791</v>
+        <v>693</v>
       </c>
       <c r="C673" s="1" t="s">
         <v>694</v>
@@ -14843,7 +14858,7 @@
         <v>1167</v>
       </c>
       <c r="B674" s="2" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="C674" s="1" t="s">
         <v>694</v>
@@ -14865,7 +14880,7 @@
         <v>1169</v>
       </c>
       <c r="B676" s="2" t="s">
-        <v>749</v>
+        <v>794</v>
       </c>
       <c r="C676" s="1" t="s">
         <v>694</v>
@@ -14876,7 +14891,7 @@
         <v>1170</v>
       </c>
       <c r="B677" s="2" t="s">
-        <v>791</v>
+        <v>749</v>
       </c>
       <c r="C677" s="1" t="s">
         <v>694</v>
@@ -14887,7 +14902,7 @@
         <v>1171</v>
       </c>
       <c r="B678" s="2" t="s">
-        <v>740</v>
+        <v>791</v>
       </c>
       <c r="C678" s="1" t="s">
         <v>694</v>
@@ -14909,21 +14924,21 @@
         <v>1173</v>
       </c>
       <c r="B680" s="2" t="s">
-        <v>1174</v>
-      </c>
-      <c r="C680" s="2" t="s">
-        <v>762</v>
+        <v>740</v>
+      </c>
+      <c r="C680" s="1" t="s">
+        <v>694</v>
       </c>
     </row>
     <row r="681" customHeight="1" spans="1:3">
       <c r="A681" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B681" s="2" t="s">
         <v>1175</v>
       </c>
-      <c r="B681" s="2" t="s">
-        <v>974</v>
-      </c>
-      <c r="C681" s="1" t="s">
-        <v>694</v>
+      <c r="C681" s="2" t="s">
+        <v>762</v>
       </c>
     </row>
     <row r="682" customHeight="1" spans="1:3">
@@ -14931,7 +14946,7 @@
         <v>1176</v>
       </c>
       <c r="B682" s="2" t="s">
-        <v>766</v>
+        <v>974</v>
       </c>
       <c r="C682" s="1" t="s">
         <v>694</v>
@@ -14942,10 +14957,10 @@
         <v>1177</v>
       </c>
       <c r="B683" s="2" t="s">
-        <v>842</v>
-      </c>
-      <c r="C683" s="2" t="s">
-        <v>762</v>
+        <v>766</v>
+      </c>
+      <c r="C683" s="1" t="s">
+        <v>694</v>
       </c>
     </row>
     <row r="684" customHeight="1" spans="1:3">
@@ -14953,10 +14968,10 @@
         <v>1178</v>
       </c>
       <c r="B684" s="2" t="s">
-        <v>889</v>
-      </c>
-      <c r="C684" s="1" t="s">
-        <v>694</v>
+        <v>842</v>
+      </c>
+      <c r="C684" s="2" t="s">
+        <v>762</v>
       </c>
     </row>
     <row r="685" customHeight="1" spans="1:3">
@@ -14964,7 +14979,7 @@
         <v>1179</v>
       </c>
       <c r="B685" s="2" t="s">
-        <v>721</v>
+        <v>889</v>
       </c>
       <c r="C685" s="1" t="s">
         <v>694</v>
@@ -14975,7 +14990,7 @@
         <v>1180</v>
       </c>
       <c r="B686" s="2" t="s">
-        <v>1181</v>
+        <v>721</v>
       </c>
       <c r="C686" s="1" t="s">
         <v>694</v>
@@ -14983,10 +14998,10 @@
     </row>
     <row r="687" customHeight="1" spans="1:3">
       <c r="A687" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B687" s="2" t="s">
         <v>1182</v>
-      </c>
-      <c r="B687" s="2" t="s">
-        <v>1183</v>
       </c>
       <c r="C687" s="1" t="s">
         <v>694</v>
@@ -14994,10 +15009,10 @@
     </row>
     <row r="688" customHeight="1" spans="1:3">
       <c r="A688" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B688" s="2" t="s">
         <v>1184</v>
-      </c>
-      <c r="B688" s="2" t="s">
-        <v>738</v>
       </c>
       <c r="C688" s="1" t="s">
         <v>694</v>
@@ -15008,7 +15023,7 @@
         <v>1185</v>
       </c>
       <c r="B689" s="2" t="s">
-        <v>1186</v>
+        <v>738</v>
       </c>
       <c r="C689" s="1" t="s">
         <v>694</v>
@@ -15016,10 +15031,10 @@
     </row>
     <row r="690" customHeight="1" spans="1:3">
       <c r="A690" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B690" s="2" t="s">
         <v>1187</v>
-      </c>
-      <c r="B690" s="2" t="s">
-        <v>794</v>
       </c>
       <c r="C690" s="1" t="s">
         <v>694</v>
@@ -15030,7 +15045,7 @@
         <v>1188</v>
       </c>
       <c r="B691" s="2" t="s">
-        <v>770</v>
+        <v>794</v>
       </c>
       <c r="C691" s="1" t="s">
         <v>694</v>
@@ -15041,7 +15056,7 @@
         <v>1189</v>
       </c>
       <c r="B692" s="2" t="s">
-        <v>1190</v>
+        <v>770</v>
       </c>
       <c r="C692" s="1" t="s">
         <v>694</v>
@@ -15049,10 +15064,10 @@
     </row>
     <row r="693" customHeight="1" spans="1:3">
       <c r="A693" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B693" s="2" t="s">
         <v>1191</v>
-      </c>
-      <c r="B693" s="2" t="s">
-        <v>738</v>
       </c>
       <c r="C693" s="1" t="s">
         <v>694</v>
@@ -15063,7 +15078,7 @@
         <v>1192</v>
       </c>
       <c r="B694" s="2" t="s">
-        <v>974</v>
+        <v>738</v>
       </c>
       <c r="C694" s="1" t="s">
         <v>694</v>
@@ -15074,9 +15089,9 @@
         <v>1193</v>
       </c>
       <c r="B695" s="2" t="s">
-        <v>999</v>
-      </c>
-      <c r="C695" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="C695" s="1" t="s">
         <v>694</v>
       </c>
     </row>
@@ -15085,9 +15100,9 @@
         <v>1194</v>
       </c>
       <c r="B696" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="C696" s="1" t="s">
+        <v>999</v>
+      </c>
+      <c r="C696" s="2" t="s">
         <v>694</v>
       </c>
     </row>
@@ -15096,7 +15111,7 @@
         <v>1195</v>
       </c>
       <c r="B697" s="2" t="s">
-        <v>1196</v>
+        <v>735</v>
       </c>
       <c r="C697" s="1" t="s">
         <v>694</v>
@@ -15104,10 +15119,10 @@
     </row>
     <row r="698" customHeight="1" spans="1:3">
       <c r="A698" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B698" s="2" t="s">
         <v>1197</v>
-      </c>
-      <c r="B698" s="2" t="s">
-        <v>1196</v>
       </c>
       <c r="C698" s="1" t="s">
         <v>694</v>
@@ -15118,7 +15133,7 @@
         <v>1198</v>
       </c>
       <c r="B699" s="2" t="s">
-        <v>802</v>
+        <v>1197</v>
       </c>
       <c r="C699" s="1" t="s">
         <v>694</v>
@@ -15129,7 +15144,7 @@
         <v>1199</v>
       </c>
       <c r="B700" s="2" t="s">
-        <v>742</v>
+        <v>802</v>
       </c>
       <c r="C700" s="1" t="s">
         <v>694</v>
@@ -15140,7 +15155,7 @@
         <v>1200</v>
       </c>
       <c r="B701" s="2" t="s">
-        <v>1201</v>
+        <v>742</v>
       </c>
       <c r="C701" s="1" t="s">
         <v>694</v>
@@ -15148,10 +15163,10 @@
     </row>
     <row r="702" customHeight="1" spans="1:3">
       <c r="A702" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B702" s="2" t="s">
         <v>1202</v>
-      </c>
-      <c r="B702" s="2" t="s">
-        <v>794</v>
       </c>
       <c r="C702" s="1" t="s">
         <v>694</v>
@@ -15162,7 +15177,7 @@
         <v>1203</v>
       </c>
       <c r="B703" s="2" t="s">
-        <v>751</v>
+        <v>794</v>
       </c>
       <c r="C703" s="1" t="s">
         <v>694</v>
@@ -15173,7 +15188,7 @@
         <v>1204</v>
       </c>
       <c r="B704" s="2" t="s">
-        <v>709</v>
+        <v>751</v>
       </c>
       <c r="C704" s="1" t="s">
         <v>694</v>
@@ -15184,9 +15199,9 @@
         <v>1205</v>
       </c>
       <c r="B705" s="2" t="s">
-        <v>945</v>
-      </c>
-      <c r="C705" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="C705" s="1" t="s">
         <v>694</v>
       </c>
     </row>
@@ -15195,10 +15210,10 @@
         <v>1206</v>
       </c>
       <c r="B706" s="2" t="s">
-        <v>1049</v>
+        <v>945</v>
       </c>
       <c r="C706" s="2" t="s">
-        <v>970</v>
+        <v>694</v>
       </c>
     </row>
     <row r="707" customHeight="1" spans="1:3">
@@ -15206,10 +15221,10 @@
         <v>1207</v>
       </c>
       <c r="B707" s="2" t="s">
-        <v>749</v>
+        <v>1049</v>
       </c>
       <c r="C707" s="2" t="s">
-        <v>694</v>
+        <v>970</v>
       </c>
     </row>
     <row r="708" customHeight="1" spans="1:3">
@@ -15217,9 +15232,9 @@
         <v>1208</v>
       </c>
       <c r="B708" s="2" t="s">
-        <v>766</v>
-      </c>
-      <c r="C708" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="C708" s="2" t="s">
         <v>694</v>
       </c>
     </row>
@@ -15239,7 +15254,7 @@
         <v>1210</v>
       </c>
       <c r="B710" s="2" t="s">
-        <v>954</v>
+        <v>766</v>
       </c>
       <c r="C710" s="1" t="s">
         <v>694</v>
@@ -15250,7 +15265,7 @@
         <v>1211</v>
       </c>
       <c r="B711" s="2" t="s">
-        <v>1212</v>
+        <v>954</v>
       </c>
       <c r="C711" s="1" t="s">
         <v>694</v>
@@ -15258,10 +15273,10 @@
     </row>
     <row r="712" customHeight="1" spans="1:3">
       <c r="A712" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B712" s="2" t="s">
         <v>1213</v>
-      </c>
-      <c r="B712" s="2" t="s">
-        <v>749</v>
       </c>
       <c r="C712" s="1" t="s">
         <v>694</v>
@@ -15272,7 +15287,7 @@
         <v>1214</v>
       </c>
       <c r="B713" s="2" t="s">
-        <v>1215</v>
+        <v>749</v>
       </c>
       <c r="C713" s="1" t="s">
         <v>694</v>
@@ -15280,10 +15295,10 @@
     </row>
     <row r="714" customHeight="1" spans="1:3">
       <c r="A714" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B714" s="2" t="s">
         <v>1216</v>
-      </c>
-      <c r="B714" s="2" t="s">
-        <v>791</v>
       </c>
       <c r="C714" s="1" t="s">
         <v>694</v>
@@ -15294,7 +15309,7 @@
         <v>1217</v>
       </c>
       <c r="B715" s="2" t="s">
-        <v>1016</v>
+        <v>791</v>
       </c>
       <c r="C715" s="1" t="s">
         <v>694</v>
@@ -15305,7 +15320,7 @@
         <v>1218</v>
       </c>
       <c r="B716" s="2" t="s">
-        <v>974</v>
+        <v>1016</v>
       </c>
       <c r="C716" s="1" t="s">
         <v>694</v>
@@ -15316,7 +15331,7 @@
         <v>1219</v>
       </c>
       <c r="B717" s="2" t="s">
-        <v>698</v>
+        <v>974</v>
       </c>
       <c r="C717" s="1" t="s">
         <v>694</v>
@@ -15327,7 +15342,7 @@
         <v>1220</v>
       </c>
       <c r="B718" s="2" t="s">
-        <v>1221</v>
+        <v>698</v>
       </c>
       <c r="C718" s="1" t="s">
         <v>694</v>
@@ -15335,12 +15350,12 @@
     </row>
     <row r="719" customHeight="1" spans="1:3">
       <c r="A719" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B719" s="2" t="s">
         <v>1222</v>
       </c>
-      <c r="B719" s="2" t="s">
-        <v>860</v>
-      </c>
-      <c r="C719" s="2" t="s">
+      <c r="C719" s="1" t="s">
         <v>694</v>
       </c>
     </row>
@@ -15349,18 +15364,18 @@
         <v>1223</v>
       </c>
       <c r="B720" s="2" t="s">
-        <v>1224</v>
-      </c>
-      <c r="C720" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="C720" s="2" t="s">
         <v>694</v>
       </c>
     </row>
     <row r="721" customHeight="1" spans="1:3">
       <c r="A721" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B721" s="2" t="s">
         <v>1225</v>
-      </c>
-      <c r="B721" s="2" t="s">
-        <v>698</v>
       </c>
       <c r="C721" s="1" t="s">
         <v>694</v>
@@ -15371,7 +15386,7 @@
         <v>1226</v>
       </c>
       <c r="B722" s="2" t="s">
-        <v>1227</v>
+        <v>698</v>
       </c>
       <c r="C722" s="1" t="s">
         <v>694</v>
@@ -15379,10 +15394,10 @@
     </row>
     <row r="723" customHeight="1" spans="1:3">
       <c r="A723" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B723" s="2" t="s">
         <v>1228</v>
-      </c>
-      <c r="B723" s="2" t="s">
-        <v>740</v>
       </c>
       <c r="C723" s="1" t="s">
         <v>694</v>
@@ -15393,7 +15408,7 @@
         <v>1229</v>
       </c>
       <c r="B724" s="2" t="s">
-        <v>921</v>
+        <v>740</v>
       </c>
       <c r="C724" s="1" t="s">
         <v>694</v>
@@ -15404,7 +15419,7 @@
         <v>1230</v>
       </c>
       <c r="B725" s="2" t="s">
-        <v>768</v>
+        <v>921</v>
       </c>
       <c r="C725" s="1" t="s">
         <v>694</v>
@@ -15415,7 +15430,7 @@
         <v>1231</v>
       </c>
       <c r="B726" s="2" t="s">
-        <v>802</v>
+        <v>768</v>
       </c>
       <c r="C726" s="1" t="s">
         <v>694</v>
@@ -15426,7 +15441,7 @@
         <v>1232</v>
       </c>
       <c r="B727" s="2" t="s">
-        <v>862</v>
+        <v>802</v>
       </c>
       <c r="C727" s="1" t="s">
         <v>694</v>
@@ -15437,7 +15452,7 @@
         <v>1233</v>
       </c>
       <c r="B728" s="2" t="s">
-        <v>1234</v>
+        <v>862</v>
       </c>
       <c r="C728" s="1" t="s">
         <v>694</v>
@@ -15445,32 +15460,32 @@
     </row>
     <row r="729" customHeight="1" spans="1:3">
       <c r="A729" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B729" s="2" t="s">
         <v>1235</v>
       </c>
-      <c r="B729" s="2" t="s">
-        <v>1236</v>
-      </c>
-      <c r="C729" s="2" t="s">
-        <v>762</v>
+      <c r="C729" s="1" t="s">
+        <v>694</v>
       </c>
     </row>
     <row r="730" customHeight="1" spans="1:3">
       <c r="A730" s="2" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B730" s="2" t="s">
         <v>1237</v>
       </c>
-      <c r="B730" s="2" t="s">
-        <v>1238</v>
-      </c>
-      <c r="C730" s="1" t="s">
-        <v>694</v>
+      <c r="C730" s="2" t="s">
+        <v>762</v>
       </c>
     </row>
     <row r="731" customHeight="1" spans="1:3">
       <c r="A731" s="2" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="B731" s="2" t="s">
-        <v>740</v>
+        <v>1239</v>
       </c>
       <c r="C731" s="1" t="s">
         <v>694</v>
@@ -15478,21 +15493,21 @@
     </row>
     <row r="732" customHeight="1" spans="1:3">
       <c r="A732" s="2" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="B732" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="C732" s="1" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="733" customHeight="1" spans="1:3">
+      <c r="A733" s="2" t="s">
         <v>1240</v>
       </c>
-      <c r="C732" s="2" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="733" customHeight="1" spans="1:3">
-      <c r="A733" s="25" t="s">
+      <c r="B733" s="2" t="s">
         <v>1241</v>
-      </c>
-      <c r="B733" s="2" t="s">
-        <v>1242</v>
       </c>
       <c r="C733" s="1" t="s">
         <v>694</v>
@@ -15500,24 +15515,24 @@
     </row>
     <row r="734" customHeight="1" spans="1:3">
       <c r="A734" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B734" s="2" t="s">
         <v>1243</v>
       </c>
-      <c r="B734" s="2" t="s">
-        <v>698</v>
-      </c>
-      <c r="C734" s="1" t="s">
-        <v>694</v>
+      <c r="C734" s="2" t="s">
+        <v>762</v>
       </c>
     </row>
     <row r="735" customHeight="1" spans="1:3">
-      <c r="A735" s="2" t="s">
+      <c r="A735" s="25" t="s">
         <v>1244</v>
       </c>
       <c r="B735" s="2" t="s">
         <v>1245</v>
       </c>
-      <c r="C735" s="2" t="s">
-        <v>970</v>
+      <c r="C735" s="1" t="s">
+        <v>694</v>
       </c>
     </row>
     <row r="736" customHeight="1" spans="1:3">
@@ -15527,8 +15542,8 @@
       <c r="B736" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="C736" s="2" t="s">
-        <v>762</v>
+      <c r="C736" s="1" t="s">
+        <v>694</v>
       </c>
     </row>
     <row r="737" customHeight="1" spans="1:3">
@@ -15536,32 +15551,32 @@
         <v>1247</v>
       </c>
       <c r="B737" s="2" t="s">
-        <v>876</v>
+        <v>1248</v>
       </c>
       <c r="C737" s="2" t="s">
-        <v>762</v>
+        <v>970</v>
       </c>
     </row>
     <row r="738" customHeight="1" spans="1:3">
       <c r="A738" s="2" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B738" s="2" t="s">
-        <v>738</v>
-      </c>
-      <c r="C738" s="1" t="s">
-        <v>694</v>
+        <v>698</v>
+      </c>
+      <c r="C738" s="2" t="s">
+        <v>762</v>
       </c>
     </row>
     <row r="739" customHeight="1" spans="1:3">
       <c r="A739" s="2" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B739" s="2" t="s">
-        <v>1250</v>
-      </c>
-      <c r="C739" s="1" t="s">
-        <v>694</v>
+        <v>876</v>
+      </c>
+      <c r="C739" s="2" t="s">
+        <v>762</v>
       </c>
     </row>
     <row r="740" customHeight="1" spans="1:3">
@@ -15569,7 +15584,7 @@
         <v>1251</v>
       </c>
       <c r="B740" s="2" t="s">
-        <v>910</v>
+        <v>738</v>
       </c>
       <c r="C740" s="1" t="s">
         <v>694</v>
@@ -15580,7 +15595,7 @@
         <v>1252</v>
       </c>
       <c r="B741" s="2" t="s">
-        <v>1116</v>
+        <v>1253</v>
       </c>
       <c r="C741" s="1" t="s">
         <v>694</v>
@@ -15588,24 +15603,24 @@
     </row>
     <row r="742" customHeight="1" spans="1:3">
       <c r="A742" s="2" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="B742" s="2" t="s">
-        <v>1123</v>
-      </c>
-      <c r="C742" s="2" t="s">
-        <v>970</v>
+        <v>910</v>
+      </c>
+      <c r="C742" s="1" t="s">
+        <v>694</v>
       </c>
     </row>
     <row r="743" customHeight="1" spans="1:3">
       <c r="A743" s="2" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B743" s="2" t="s">
-        <v>1255</v>
-      </c>
-      <c r="C743" s="2" t="s">
-        <v>762</v>
+        <v>1117</v>
+      </c>
+      <c r="C743" s="1" t="s">
+        <v>694</v>
       </c>
     </row>
     <row r="744" customHeight="1" spans="1:3">
@@ -15613,10 +15628,10 @@
         <v>1256</v>
       </c>
       <c r="B744" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="C744" s="1" t="s">
-        <v>694</v>
+        <v>1124</v>
+      </c>
+      <c r="C744" s="2" t="s">
+        <v>970</v>
       </c>
     </row>
     <row r="745" customHeight="1" spans="1:3">
@@ -15624,18 +15639,18 @@
         <v>1257</v>
       </c>
       <c r="B745" s="2" t="s">
-        <v>766</v>
-      </c>
-      <c r="C745" s="1" t="s">
-        <v>694</v>
+        <v>1258</v>
+      </c>
+      <c r="C745" s="2" t="s">
+        <v>762</v>
       </c>
     </row>
     <row r="746" customHeight="1" spans="1:3">
       <c r="A746" s="2" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B746" s="2" t="s">
-        <v>735</v>
+        <v>759</v>
       </c>
       <c r="C746" s="1" t="s">
         <v>694</v>
@@ -15643,10 +15658,10 @@
     </row>
     <row r="747" customHeight="1" spans="1:3">
       <c r="A747" s="2" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B747" s="2" t="s">
-        <v>802</v>
+        <v>766</v>
       </c>
       <c r="C747" s="1" t="s">
         <v>694</v>
@@ -15654,10 +15669,10 @@
     </row>
     <row r="748" customHeight="1" spans="1:3">
       <c r="A748" s="2" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="B748" s="2" t="s">
-        <v>770</v>
+        <v>735</v>
       </c>
       <c r="C748" s="1" t="s">
         <v>694</v>
@@ -15665,10 +15680,10 @@
     </row>
     <row r="749" customHeight="1" spans="1:3">
       <c r="A749" s="2" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="B749" s="2" t="s">
-        <v>860</v>
+        <v>802</v>
       </c>
       <c r="C749" s="1" t="s">
         <v>694</v>
@@ -15676,10 +15691,10 @@
     </row>
     <row r="750" customHeight="1" spans="1:3">
       <c r="A750" s="2" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B750" s="2" t="s">
-        <v>1263</v>
+        <v>770</v>
       </c>
       <c r="C750" s="1" t="s">
         <v>694</v>
@@ -15690,9 +15705,9 @@
         <v>1264</v>
       </c>
       <c r="B751" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="C751" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="C751" s="1" t="s">
         <v>694</v>
       </c>
     </row>
@@ -15701,18 +15716,18 @@
         <v>1265</v>
       </c>
       <c r="B752" s="2" t="s">
-        <v>742</v>
-      </c>
-      <c r="C752" s="2" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C752" s="1" t="s">
         <v>694</v>
       </c>
     </row>
     <row r="753" customHeight="1" spans="1:4">
       <c r="A753" s="2" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="B753" s="2" t="s">
-        <v>1267</v>
+        <v>802</v>
       </c>
       <c r="C753" s="2" t="s">
         <v>694</v>
@@ -15723,7 +15738,7 @@
         <v>1268</v>
       </c>
       <c r="B754" s="2" t="s">
-        <v>717</v>
+        <v>742</v>
       </c>
       <c r="C754" s="2" t="s">
         <v>694</v>
@@ -15745,7 +15760,7 @@
         <v>1271</v>
       </c>
       <c r="B756" s="2" t="s">
-        <v>1272</v>
+        <v>717</v>
       </c>
       <c r="C756" s="2" t="s">
         <v>694</v>
@@ -15753,10 +15768,10 @@
     </row>
     <row r="757" customHeight="1" spans="1:4">
       <c r="A757" s="2" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B757" s="2" t="s">
         <v>1273</v>
-      </c>
-      <c r="B757" s="2" t="s">
-        <v>1274</v>
       </c>
       <c r="C757" s="2" t="s">
         <v>694</v>
@@ -15764,13 +15779,13 @@
     </row>
     <row r="758" customHeight="1" spans="1:4">
       <c r="A758" s="2" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B758" s="2" t="s">
         <v>1275</v>
       </c>
-      <c r="B758" s="2" t="s">
-        <v>842</v>
-      </c>
       <c r="C758" s="2" t="s">
-        <v>762</v>
+        <v>694</v>
       </c>
     </row>
     <row r="759" customHeight="1" spans="1:4">
@@ -15789,10 +15804,10 @@
         <v>1278</v>
       </c>
       <c r="B760" s="2" t="s">
-        <v>885</v>
+        <v>842</v>
       </c>
       <c r="C760" s="2" t="s">
-        <v>694</v>
+        <v>762</v>
       </c>
     </row>
     <row r="761" customHeight="1" spans="1:4">
@@ -15800,7 +15815,7 @@
         <v>1279</v>
       </c>
       <c r="B761" s="2" t="s">
-        <v>979</v>
+        <v>1280</v>
       </c>
       <c r="C761" s="2" t="s">
         <v>694</v>
@@ -15808,10 +15823,10 @@
     </row>
     <row r="762" customHeight="1" spans="1:4">
       <c r="A762" s="2" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B762" s="2" t="s">
-        <v>1281</v>
+        <v>885</v>
       </c>
       <c r="C762" s="2" t="s">
         <v>694</v>
@@ -15822,55 +15837,55 @@
         <v>1282</v>
       </c>
       <c r="B763" s="2" t="s">
+        <v>979</v>
+      </c>
+      <c r="C763" s="2" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="764" customHeight="1" spans="1:4">
+      <c r="A764" s="2" t="s">
         <v>1283</v>
       </c>
-      <c r="C763" s="2" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="764" customHeight="1" spans="1:4">
-      <c r="A764" s="13" t="s">
+      <c r="B764" s="2" t="s">
         <v>1284</v>
       </c>
-      <c r="B764" s="13" t="s">
-        <v>735</v>
-      </c>
-      <c r="C764" s="13" t="s">
-        <v>736</v>
-      </c>
-      <c r="D764" s="14"/>
+      <c r="C764" s="2" t="s">
+        <v>694</v>
+      </c>
     </row>
     <row r="765" customHeight="1" spans="1:4">
       <c r="A765" s="2" t="s">
         <v>1285</v>
       </c>
       <c r="B765" s="2" t="s">
-        <v>860</v>
+        <v>1286</v>
       </c>
       <c r="C765" s="2" t="s">
-        <v>1286</v>
+        <v>694</v>
       </c>
     </row>
     <row r="766" customHeight="1" spans="1:4">
-      <c r="A766" s="2" t="s">
+      <c r="A766" s="13" t="s">
         <v>1287</v>
       </c>
-      <c r="B766" s="2" t="s">
-        <v>717</v>
-      </c>
-      <c r="C766" s="2" t="s">
-        <v>694</v>
-      </c>
+      <c r="B766" s="13" t="s">
+        <v>735</v>
+      </c>
+      <c r="C766" s="13" t="s">
+        <v>736</v>
+      </c>
+      <c r="D766" s="14"/>
     </row>
     <row r="767" customHeight="1" spans="1:4">
       <c r="A767" s="2" t="s">
         <v>1288</v>
       </c>
       <c r="B767" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="C767" s="2" t="s">
         <v>1289</v>
-      </c>
-      <c r="C767" s="2" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="768" customHeight="1" spans="1:4">
@@ -15878,7 +15893,7 @@
         <v>1290</v>
       </c>
       <c r="B768" s="2" t="s">
-        <v>1291</v>
+        <v>717</v>
       </c>
       <c r="C768" s="2" t="s">
         <v>694</v>
@@ -15886,10 +15901,10 @@
     </row>
     <row r="769" customHeight="1" spans="1:3">
       <c r="A769" s="2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B769" s="2" t="s">
         <v>1292</v>
-      </c>
-      <c r="B769" s="2" t="s">
-        <v>1293</v>
       </c>
       <c r="C769" s="2" t="s">
         <v>694</v>
@@ -15897,13 +15912,13 @@
     </row>
     <row r="770" customHeight="1" spans="1:3">
       <c r="A770" s="2" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B770" s="2" t="s">
         <v>1294</v>
       </c>
-      <c r="B770" s="2" t="s">
-        <v>876</v>
-      </c>
       <c r="C770" s="2" t="s">
-        <v>762</v>
+        <v>694</v>
       </c>
     </row>
     <row r="771" customHeight="1" spans="1:3">
@@ -15911,7 +15926,7 @@
         <v>1295</v>
       </c>
       <c r="B771" s="2" t="s">
-        <v>740</v>
+        <v>1296</v>
       </c>
       <c r="C771" s="2" t="s">
         <v>694</v>
@@ -15919,10 +15934,10 @@
     </row>
     <row r="772" customHeight="1" spans="1:3">
       <c r="A772" s="2" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="B772" s="2" t="s">
-        <v>1297</v>
+        <v>876</v>
       </c>
       <c r="C772" s="2" t="s">
         <v>762</v>
@@ -15933,7 +15948,7 @@
         <v>1298</v>
       </c>
       <c r="B773" s="2" t="s">
-        <v>1299</v>
+        <v>740</v>
       </c>
       <c r="C773" s="2" t="s">
         <v>694</v>
@@ -15941,13 +15956,13 @@
     </row>
     <row r="774" customHeight="1" spans="1:3">
       <c r="A774" s="2" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B774" s="2" t="s">
         <v>1300</v>
       </c>
-      <c r="B774" s="2" t="s">
-        <v>707</v>
-      </c>
       <c r="C774" s="2" t="s">
-        <v>694</v>
+        <v>762</v>
       </c>
     </row>
     <row r="775" customHeight="1" spans="1:3">
@@ -15966,7 +15981,7 @@
         <v>1303</v>
       </c>
       <c r="B776" s="2" t="s">
-        <v>759</v>
+        <v>707</v>
       </c>
       <c r="C776" s="2" t="s">
         <v>694</v>
@@ -15988,7 +16003,7 @@
         <v>1306</v>
       </c>
       <c r="B778" s="2" t="s">
-        <v>1307</v>
+        <v>759</v>
       </c>
       <c r="C778" s="2" t="s">
         <v>694</v>
@@ -15996,10 +16011,10 @@
     </row>
     <row r="779" customHeight="1" spans="1:3">
       <c r="A779" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B779" s="2" t="s">
         <v>1308</v>
-      </c>
-      <c r="B779" s="2" t="s">
-        <v>751</v>
       </c>
       <c r="C779" s="2" t="s">
         <v>694</v>
@@ -16010,7 +16025,7 @@
         <v>1309</v>
       </c>
       <c r="B780" s="2" t="s">
-        <v>735</v>
+        <v>1310</v>
       </c>
       <c r="C780" s="2" t="s">
         <v>694</v>
@@ -16018,10 +16033,10 @@
     </row>
     <row r="781" customHeight="1" spans="1:3">
       <c r="A781" s="2" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="B781" s="2" t="s">
-        <v>735</v>
+        <v>751</v>
       </c>
       <c r="C781" s="2" t="s">
         <v>694</v>
@@ -16029,13 +16044,13 @@
     </row>
     <row r="782" customHeight="1" spans="1:3">
       <c r="A782" s="2" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="B782" s="2" t="s">
-        <v>1312</v>
+        <v>735</v>
       </c>
       <c r="C782" s="2" t="s">
-        <v>762</v>
+        <v>694</v>
       </c>
     </row>
     <row r="783" customHeight="1" spans="1:3">
@@ -16043,7 +16058,7 @@
         <v>1313</v>
       </c>
       <c r="B783" s="2" t="s">
-        <v>1314</v>
+        <v>735</v>
       </c>
       <c r="C783" s="2" t="s">
         <v>694</v>
@@ -16051,13 +16066,13 @@
     </row>
     <row r="784" customHeight="1" spans="1:3">
       <c r="A784" s="2" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B784" s="2" t="s">
         <v>1315</v>
       </c>
-      <c r="B784" s="2" t="s">
-        <v>999</v>
-      </c>
       <c r="C784" s="2" t="s">
-        <v>694</v>
+        <v>762</v>
       </c>
     </row>
     <row r="785" customHeight="1" spans="1:4">
@@ -16076,7 +16091,7 @@
         <v>1318</v>
       </c>
       <c r="B786" s="2" t="s">
-        <v>939</v>
+        <v>999</v>
       </c>
       <c r="C786" s="2" t="s">
         <v>694</v>
@@ -16098,7 +16113,7 @@
         <v>1321</v>
       </c>
       <c r="B788" s="2" t="s">
-        <v>887</v>
+        <v>939</v>
       </c>
       <c r="C788" s="2" t="s">
         <v>694</v>
@@ -16120,52 +16135,52 @@
         <v>1324</v>
       </c>
       <c r="B790" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="C790" s="2" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="791" customHeight="1" spans="1:4">
+      <c r="A791" s="2" t="s">
         <v>1325</v>
       </c>
-      <c r="C790" s="2" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="791" customHeight="1" spans="1:4">
-      <c r="A791" s="13" t="s">
+      <c r="B791" s="2" t="s">
         <v>1326</v>
       </c>
-      <c r="B791" s="13" t="s">
-        <v>1327</v>
-      </c>
-      <c r="C791" s="13" t="s">
-        <v>702</v>
-      </c>
-      <c r="D791" s="14"/>
+      <c r="C791" s="2" t="s">
+        <v>694</v>
+      </c>
     </row>
     <row r="792" customHeight="1" spans="1:4">
       <c r="A792" s="2" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B792" s="2" t="s">
         <v>1328</v>
       </c>
-      <c r="B792" s="2" t="s">
-        <v>876</v>
-      </c>
       <c r="C792" s="2" t="s">
         <v>694</v>
       </c>
     </row>
     <row r="793" customHeight="1" spans="1:4">
-      <c r="A793" s="2" t="s">
+      <c r="A793" s="13" t="s">
         <v>1329</v>
       </c>
-      <c r="B793" s="2" t="s">
-        <v>742</v>
-      </c>
-      <c r="C793" s="2" t="s">
-        <v>694</v>
-      </c>
+      <c r="B793" s="13" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C793" s="13" t="s">
+        <v>702</v>
+      </c>
+      <c r="D793" s="14"/>
     </row>
     <row r="794" customHeight="1" spans="1:4">
       <c r="A794" s="2" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="B794" s="2" t="s">
-        <v>1046</v>
+        <v>876</v>
       </c>
       <c r="C794" s="2" t="s">
         <v>694</v>
@@ -16173,10 +16188,10 @@
     </row>
     <row r="795" customHeight="1" spans="1:4">
       <c r="A795" s="2" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="B795" s="2" t="s">
-        <v>876</v>
+        <v>742</v>
       </c>
       <c r="C795" s="2" t="s">
         <v>694</v>
@@ -16184,21 +16199,21 @@
     </row>
     <row r="796" customHeight="1" spans="1:4">
       <c r="A796" s="2" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="B796" s="2" t="s">
-        <v>988</v>
+        <v>1046</v>
       </c>
       <c r="C796" s="2" t="s">
-        <v>762</v>
+        <v>694</v>
       </c>
     </row>
     <row r="797" customHeight="1" spans="1:4">
       <c r="A797" s="2" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="B797" s="2" t="s">
-        <v>1334</v>
+        <v>876</v>
       </c>
       <c r="C797" s="2" t="s">
         <v>694</v>
@@ -16209,10 +16224,10 @@
         <v>1335</v>
       </c>
       <c r="B798" s="2" t="s">
-        <v>876</v>
+        <v>988</v>
       </c>
       <c r="C798" s="2" t="s">
-        <v>694</v>
+        <v>762</v>
       </c>
     </row>
     <row r="799" customHeight="1" spans="1:4">
@@ -16220,7 +16235,7 @@
         <v>1336</v>
       </c>
       <c r="B799" s="2" t="s">
-        <v>1314</v>
+        <v>1337</v>
       </c>
       <c r="C799" s="2" t="s">
         <v>694</v>
@@ -16228,10 +16243,10 @@
     </row>
     <row r="800" customHeight="1" spans="1:4">
       <c r="A800" s="2" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="B800" s="2" t="s">
-        <v>974</v>
+        <v>876</v>
       </c>
       <c r="C800" s="2" t="s">
         <v>694</v>
@@ -16239,10 +16254,10 @@
     </row>
     <row r="801" customHeight="1" spans="1:3">
       <c r="A801" s="2" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="B801" s="2" t="s">
-        <v>770</v>
+        <v>1317</v>
       </c>
       <c r="C801" s="2" t="s">
         <v>694</v>
@@ -16250,13 +16265,13 @@
     </row>
     <row r="802" customHeight="1" spans="1:3">
       <c r="A802" s="2" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="B802" s="2" t="s">
-        <v>1340</v>
+        <v>974</v>
       </c>
       <c r="C802" s="2" t="s">
-        <v>762</v>
+        <v>694</v>
       </c>
     </row>
     <row r="803" customHeight="1" spans="1:3">
@@ -16275,18 +16290,18 @@
         <v>1342</v>
       </c>
       <c r="B804" s="2" t="s">
-        <v>693</v>
+        <v>1343</v>
       </c>
       <c r="C804" s="2" t="s">
-        <v>694</v>
+        <v>762</v>
       </c>
     </row>
     <row r="805" customHeight="1" spans="1:3">
       <c r="A805" s="2" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B805" s="2" t="s">
-        <v>1132</v>
+        <v>770</v>
       </c>
       <c r="C805" s="2" t="s">
         <v>694</v>
@@ -16294,10 +16309,10 @@
     </row>
     <row r="806" customHeight="1" spans="1:3">
       <c r="A806" s="2" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B806" s="2" t="s">
-        <v>1345</v>
+        <v>693</v>
       </c>
       <c r="C806" s="2" t="s">
         <v>694</v>
@@ -16308,7 +16323,7 @@
         <v>1346</v>
       </c>
       <c r="B807" s="2" t="s">
-        <v>766</v>
+        <v>1133</v>
       </c>
       <c r="C807" s="2" t="s">
         <v>694</v>
@@ -16319,7 +16334,7 @@
         <v>1347</v>
       </c>
       <c r="B808" s="2" t="s">
-        <v>766</v>
+        <v>1348</v>
       </c>
       <c r="C808" s="2" t="s">
         <v>694</v>
@@ -16327,10 +16342,10 @@
     </row>
     <row r="809" customHeight="1" spans="1:3">
       <c r="A809" s="2" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="B809" s="2" t="s">
-        <v>804</v>
+        <v>766</v>
       </c>
       <c r="C809" s="2" t="s">
         <v>694</v>
@@ -16338,10 +16353,10 @@
     </row>
     <row r="810" customHeight="1" spans="1:3">
       <c r="A810" s="2" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B810" s="2" t="s">
-        <v>1350</v>
+        <v>766</v>
       </c>
       <c r="C810" s="2" t="s">
         <v>694</v>
@@ -16352,7 +16367,7 @@
         <v>1351</v>
       </c>
       <c r="B811" s="2" t="s">
-        <v>698</v>
+        <v>804</v>
       </c>
       <c r="C811" s="2" t="s">
         <v>694</v>
@@ -16363,7 +16378,7 @@
         <v>1352</v>
       </c>
       <c r="B812" s="2" t="s">
-        <v>933</v>
+        <v>1353</v>
       </c>
       <c r="C812" s="2" t="s">
         <v>694</v>
@@ -16371,10 +16386,10 @@
     </row>
     <row r="813" customHeight="1" spans="1:3">
       <c r="A813" s="2" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B813" s="2" t="s">
-        <v>717</v>
+        <v>698</v>
       </c>
       <c r="C813" s="2" t="s">
         <v>694</v>
@@ -16382,10 +16397,10 @@
     </row>
     <row r="814" customHeight="1" spans="1:3">
       <c r="A814" s="2" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="B814" s="2" t="s">
-        <v>1016</v>
+        <v>933</v>
       </c>
       <c r="C814" s="2" t="s">
         <v>694</v>
@@ -16393,10 +16408,10 @@
     </row>
     <row r="815" customHeight="1" spans="1:3">
       <c r="A815" s="2" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="B815" s="2" t="s">
-        <v>1356</v>
+        <v>717</v>
       </c>
       <c r="C815" s="2" t="s">
         <v>694</v>
@@ -16407,52 +16422,52 @@
         <v>1357</v>
       </c>
       <c r="B816" s="2" t="s">
-        <v>751</v>
+        <v>1016</v>
       </c>
       <c r="C816" s="2" t="s">
         <v>694</v>
       </c>
     </row>
     <row r="817" customHeight="1" spans="1:4">
-      <c r="A817" s="13" t="s">
+      <c r="A817" s="2" t="s">
         <v>1358</v>
       </c>
-      <c r="B817" s="13" t="s">
-        <v>735</v>
-      </c>
-      <c r="C817" s="13" t="s">
-        <v>736</v>
-      </c>
-      <c r="D817" s="14"/>
+      <c r="B817" s="2" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C817" s="2" t="s">
+        <v>694</v>
+      </c>
     </row>
     <row r="818" customHeight="1" spans="1:4">
       <c r="A818" s="2" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="B818" s="2" t="s">
-        <v>999</v>
+        <v>751</v>
       </c>
       <c r="C818" s="2" t="s">
         <v>694</v>
       </c>
     </row>
     <row r="819" customHeight="1" spans="1:4">
-      <c r="A819" s="2" t="s">
-        <v>1360</v>
-      </c>
-      <c r="B819" s="2" t="s">
-        <v>698</v>
-      </c>
-      <c r="C819" s="2" t="s">
-        <v>694</v>
-      </c>
+      <c r="A819" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B819" s="13" t="s">
+        <v>735</v>
+      </c>
+      <c r="C819" s="13" t="s">
+        <v>736</v>
+      </c>
+      <c r="D819" s="14"/>
     </row>
     <row r="820" customHeight="1" spans="1:4">
       <c r="A820" s="2" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B820" s="2" t="s">
-        <v>742</v>
+        <v>999</v>
       </c>
       <c r="C820" s="2" t="s">
         <v>694</v>
@@ -16460,10 +16475,10 @@
     </row>
     <row r="821" customHeight="1" spans="1:4">
       <c r="A821" s="2" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="B821" s="2" t="s">
-        <v>1084</v>
+        <v>698</v>
       </c>
       <c r="C821" s="2" t="s">
         <v>694</v>
@@ -16471,10 +16486,10 @@
     </row>
     <row r="822" customHeight="1" spans="1:4">
       <c r="A822" s="2" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B822" s="2" t="s">
-        <v>768</v>
+        <v>742</v>
       </c>
       <c r="C822" s="2" t="s">
         <v>694</v>
@@ -16482,10 +16497,10 @@
     </row>
     <row r="823" customHeight="1" spans="1:4">
       <c r="A823" s="2" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="B823" s="2" t="s">
-        <v>910</v>
+        <v>1084</v>
       </c>
       <c r="C823" s="2" t="s">
         <v>694</v>
@@ -16493,10 +16508,10 @@
     </row>
     <row r="824" customHeight="1" spans="1:4">
       <c r="A824" s="2" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B824" s="2" t="s">
-        <v>804</v>
+        <v>768</v>
       </c>
       <c r="C824" s="2" t="s">
         <v>694</v>
@@ -16504,10 +16519,10 @@
     </row>
     <row r="825" customHeight="1" spans="1:4">
       <c r="A825" s="2" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="B825" s="2" t="s">
-        <v>791</v>
+        <v>910</v>
       </c>
       <c r="C825" s="2" t="s">
         <v>694</v>
@@ -16515,10 +16530,10 @@
     </row>
     <row r="826" customHeight="1" spans="1:4">
       <c r="A826" s="2" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="B826" s="2" t="s">
-        <v>1368</v>
+        <v>804</v>
       </c>
       <c r="C826" s="2" t="s">
         <v>694</v>
@@ -16529,7 +16544,7 @@
         <v>1369</v>
       </c>
       <c r="B827" s="2" t="s">
-        <v>717</v>
+        <v>791</v>
       </c>
       <c r="C827" s="2" t="s">
         <v>694</v>
@@ -16540,7 +16555,7 @@
         <v>1370</v>
       </c>
       <c r="B828" s="2" t="s">
-        <v>802</v>
+        <v>1371</v>
       </c>
       <c r="C828" s="2" t="s">
         <v>694</v>
@@ -16548,10 +16563,10 @@
     </row>
     <row r="829" customHeight="1" spans="1:4">
       <c r="A829" s="2" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="B829" s="2" t="s">
-        <v>1372</v>
+        <v>717</v>
       </c>
       <c r="C829" s="2" t="s">
         <v>694</v>
@@ -16562,7 +16577,7 @@
         <v>1373</v>
       </c>
       <c r="B830" s="2" t="s">
-        <v>1374</v>
+        <v>802</v>
       </c>
       <c r="C830" s="2" t="s">
         <v>694</v>
@@ -16570,10 +16585,10 @@
     </row>
     <row r="831" customHeight="1" spans="1:4">
       <c r="A831" s="2" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B831" s="2" t="s">
         <v>1375</v>
-      </c>
-      <c r="B831" s="2" t="s">
-        <v>1376</v>
       </c>
       <c r="C831" s="2" t="s">
         <v>694</v>
@@ -16581,10 +16596,10 @@
     </row>
     <row r="832" customHeight="1" spans="1:4">
       <c r="A832" s="2" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B832" s="2" t="s">
         <v>1377</v>
-      </c>
-      <c r="B832" s="2" t="s">
-        <v>791</v>
       </c>
       <c r="C832" s="2" t="s">
         <v>694</v>
@@ -16606,7 +16621,7 @@
         <v>1380</v>
       </c>
       <c r="B834" s="2" t="s">
-        <v>698</v>
+        <v>791</v>
       </c>
       <c r="C834" s="2" t="s">
         <v>694</v>
@@ -16617,7 +16632,7 @@
         <v>1381</v>
       </c>
       <c r="B835" s="2" t="s">
-        <v>742</v>
+        <v>1382</v>
       </c>
       <c r="C835" s="2" t="s">
         <v>694</v>
@@ -16625,60 +16640,60 @@
     </row>
     <row r="836" customHeight="1" spans="1:4">
       <c r="A836" s="2" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="B836" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="C836" s="2" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="837" customHeight="1" spans="1:4">
+      <c r="A837" s="2" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B837" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="C837" s="2" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="838" customHeight="1" spans="1:4">
+      <c r="A838" s="2" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B838" s="2" t="s">
         <v>749</v>
       </c>
-      <c r="C836" s="2" t="s">
+      <c r="C838" s="2" t="s">
         <v>762</v>
       </c>
     </row>
-    <row r="837" customHeight="1" spans="1:4">
-      <c r="A837" s="13" t="s">
-        <v>1383</v>
-      </c>
-      <c r="B837" s="13" t="s">
-        <v>1384</v>
-      </c>
-      <c r="C837" s="13" t="s">
+    <row r="839" customHeight="1" spans="1:4">
+      <c r="A839" s="13" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B839" s="13" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C839" s="13" t="s">
         <v>705</v>
       </c>
-      <c r="D837" s="14"/>
-    </row>
-    <row r="838" customHeight="1" spans="1:4">
-      <c r="A838" s="13" t="s">
-        <v>1385</v>
-      </c>
-      <c r="B838" s="13" t="s">
+      <c r="D839" s="14"/>
+    </row>
+    <row r="840" customHeight="1" spans="1:4">
+      <c r="A840" s="13" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B840" s="13" t="s">
         <v>979</v>
       </c>
-      <c r="C838" s="13" t="s">
+      <c r="C840" s="13" t="s">
         <v>736</v>
       </c>
-      <c r="D838" s="14"/>
-    </row>
-    <row r="839" customHeight="1" spans="1:4">
-      <c r="A839" s="2" t="s">
-        <v>1386</v>
-      </c>
-      <c r="B839" s="2" t="s">
-        <v>1387</v>
-      </c>
-      <c r="C839" s="2" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="840" customHeight="1" spans="1:4">
-      <c r="A840" s="2" t="s">
-        <v>1388</v>
-      </c>
-      <c r="B840" s="2" t="s">
-        <v>693</v>
-      </c>
-      <c r="C840" s="2" t="s">
-        <v>694</v>
-      </c>
+      <c r="D840" s="14"/>
     </row>
     <row r="841" customHeight="1" spans="1:4">
       <c r="A841" s="2" t="s">
@@ -16688,7 +16703,7 @@
         <v>1390</v>
       </c>
       <c r="C841" s="2" t="s">
-        <v>694</v>
+        <v>762</v>
       </c>
     </row>
     <row r="842" customHeight="1" spans="1:4">
@@ -16696,7 +16711,7 @@
         <v>1391</v>
       </c>
       <c r="B842" s="2" t="s">
-        <v>885</v>
+        <v>693</v>
       </c>
       <c r="C842" s="2" t="s">
         <v>694</v>
@@ -16707,7 +16722,7 @@
         <v>1392</v>
       </c>
       <c r="B843" s="2" t="s">
-        <v>831</v>
+        <v>1393</v>
       </c>
       <c r="C843" s="2" t="s">
         <v>694</v>
@@ -16715,10 +16730,10 @@
     </row>
     <row r="844" customHeight="1" spans="1:4">
       <c r="A844" s="2" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="B844" s="2" t="s">
-        <v>1046</v>
+        <v>885</v>
       </c>
       <c r="C844" s="2" t="s">
         <v>694</v>
@@ -16726,10 +16741,10 @@
     </row>
     <row r="845" customHeight="1" spans="1:4">
       <c r="A845" s="2" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="B845" s="2" t="s">
-        <v>717</v>
+        <v>831</v>
       </c>
       <c r="C845" s="2" t="s">
         <v>694</v>
@@ -16737,10 +16752,10 @@
     </row>
     <row r="846" customHeight="1" spans="1:4">
       <c r="A846" s="2" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="B846" s="2" t="s">
-        <v>1299</v>
+        <v>1046</v>
       </c>
       <c r="C846" s="2" t="s">
         <v>694</v>
@@ -16748,10 +16763,10 @@
     </row>
     <row r="847" customHeight="1" spans="1:4">
       <c r="A847" s="2" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="B847" s="2" t="s">
-        <v>698</v>
+        <v>717</v>
       </c>
       <c r="C847" s="2" t="s">
         <v>694</v>
@@ -16759,10 +16774,10 @@
     </row>
     <row r="848" customHeight="1" spans="1:4">
       <c r="A848" s="2" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="B848" s="2" t="s">
-        <v>1314</v>
+        <v>1302</v>
       </c>
       <c r="C848" s="2" t="s">
         <v>694</v>
@@ -16770,10 +16785,10 @@
     </row>
     <row r="849" customHeight="1" spans="1:3">
       <c r="A849" s="2" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="B849" s="2" t="s">
-        <v>742</v>
+        <v>698</v>
       </c>
       <c r="C849" s="2" t="s">
         <v>694</v>
@@ -16781,10 +16796,10 @@
     </row>
     <row r="850" customHeight="1" spans="1:3">
       <c r="A850" s="2" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="B850" s="2" t="s">
-        <v>919</v>
+        <v>1317</v>
       </c>
       <c r="C850" s="2" t="s">
         <v>694</v>
@@ -16792,10 +16807,10 @@
     </row>
     <row r="851" customHeight="1" spans="1:3">
       <c r="A851" s="2" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="B851" s="2" t="s">
-        <v>1401</v>
+        <v>742</v>
       </c>
       <c r="C851" s="2" t="s">
         <v>694</v>
@@ -16806,7 +16821,7 @@
         <v>1402</v>
       </c>
       <c r="B852" s="2" t="s">
-        <v>742</v>
+        <v>919</v>
       </c>
       <c r="C852" s="2" t="s">
         <v>694</v>
@@ -16817,7 +16832,7 @@
         <v>1403</v>
       </c>
       <c r="B853" s="2" t="s">
-        <v>1046</v>
+        <v>1404</v>
       </c>
       <c r="C853" s="2" t="s">
         <v>694</v>
@@ -16825,10 +16840,10 @@
     </row>
     <row r="854" customHeight="1" spans="1:3">
       <c r="A854" s="2" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="B854" s="2" t="s">
-        <v>933</v>
+        <v>742</v>
       </c>
       <c r="C854" s="2" t="s">
         <v>694</v>
@@ -16836,10 +16851,10 @@
     </row>
     <row r="855" customHeight="1" spans="1:3">
       <c r="A855" s="2" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="B855" s="2" t="s">
-        <v>794</v>
+        <v>1046</v>
       </c>
       <c r="C855" s="2" t="s">
         <v>694</v>
@@ -16847,10 +16862,10 @@
     </row>
     <row r="856" customHeight="1" spans="1:3">
       <c r="A856" s="2" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="B856" s="2" t="s">
-        <v>1186</v>
+        <v>933</v>
       </c>
       <c r="C856" s="2" t="s">
         <v>694</v>
@@ -16858,10 +16873,10 @@
     </row>
     <row r="857" customHeight="1" spans="1:3">
       <c r="A857" s="2" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="B857" s="2" t="s">
-        <v>1408</v>
+        <v>794</v>
       </c>
       <c r="C857" s="2" t="s">
         <v>694</v>
@@ -16872,7 +16887,7 @@
         <v>1409</v>
       </c>
       <c r="B858" s="2" t="s">
-        <v>802</v>
+        <v>1187</v>
       </c>
       <c r="C858" s="2" t="s">
         <v>694</v>
@@ -16883,7 +16898,7 @@
         <v>1410</v>
       </c>
       <c r="B859" s="2" t="s">
-        <v>838</v>
+        <v>1411</v>
       </c>
       <c r="C859" s="2" t="s">
         <v>694</v>
@@ -16891,21 +16906,21 @@
     </row>
     <row r="860" customHeight="1" spans="1:3">
       <c r="A860" s="2" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="B860" s="2" t="s">
-        <v>994</v>
+        <v>802</v>
       </c>
       <c r="C860" s="2" t="s">
-        <v>970</v>
+        <v>694</v>
       </c>
     </row>
     <row r="861" customHeight="1" spans="1:3">
       <c r="A861" s="2" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="B861" s="2" t="s">
-        <v>713</v>
+        <v>838</v>
       </c>
       <c r="C861" s="2" t="s">
         <v>694</v>
@@ -16913,21 +16928,21 @@
     </row>
     <row r="862" customHeight="1" spans="1:3">
       <c r="A862" s="2" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="B862" s="2" t="s">
-        <v>842</v>
+        <v>994</v>
       </c>
       <c r="C862" s="2" t="s">
-        <v>762</v>
+        <v>970</v>
       </c>
     </row>
     <row r="863" customHeight="1" spans="1:3">
       <c r="A863" s="2" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="B863" s="2" t="s">
-        <v>979</v>
+        <v>713</v>
       </c>
       <c r="C863" s="2" t="s">
         <v>694</v>
@@ -16935,13 +16950,13 @@
     </row>
     <row r="864" customHeight="1" spans="1:3">
       <c r="A864" s="2" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="B864" s="2" t="s">
-        <v>1416</v>
+        <v>842</v>
       </c>
       <c r="C864" s="2" t="s">
-        <v>694</v>
+        <v>762</v>
       </c>
     </row>
     <row r="865" customHeight="1" spans="1:3">
@@ -16949,7 +16964,7 @@
         <v>1417</v>
       </c>
       <c r="B865" s="2" t="s">
-        <v>698</v>
+        <v>979</v>
       </c>
       <c r="C865" s="2" t="s">
         <v>694</v>
@@ -16957,10 +16972,10 @@
     </row>
     <row r="866" customHeight="1" spans="1:3">
       <c r="A866" s="2" t="s">
-        <v>1046</v>
+        <v>1418</v>
       </c>
       <c r="B866" s="2" t="s">
-        <v>717</v>
+        <v>1419</v>
       </c>
       <c r="C866" s="2" t="s">
         <v>694</v>
@@ -16968,10 +16983,10 @@
     </row>
     <row r="867" customHeight="1" spans="1:3">
       <c r="A867" s="2" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="B867" s="2" t="s">
-        <v>836</v>
+        <v>698</v>
       </c>
       <c r="C867" s="2" t="s">
         <v>694</v>
@@ -16979,21 +16994,21 @@
     </row>
     <row r="868" customHeight="1" spans="1:3">
       <c r="A868" s="2" t="s">
-        <v>1419</v>
+        <v>1046</v>
       </c>
       <c r="B868" s="2" t="s">
-        <v>1302</v>
+        <v>717</v>
       </c>
       <c r="C868" s="2" t="s">
-        <v>762</v>
+        <v>694</v>
       </c>
     </row>
     <row r="869" customHeight="1" spans="1:3">
       <c r="A869" s="2" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="B869" s="2" t="s">
-        <v>933</v>
+        <v>836</v>
       </c>
       <c r="C869" s="2" t="s">
         <v>694</v>
@@ -17001,21 +17016,21 @@
     </row>
     <row r="870" customHeight="1" spans="1:3">
       <c r="A870" s="2" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="B870" s="2" t="s">
-        <v>939</v>
+        <v>1305</v>
       </c>
       <c r="C870" s="2" t="s">
-        <v>694</v>
+        <v>762</v>
       </c>
     </row>
     <row r="871" customHeight="1" spans="1:3">
       <c r="A871" s="2" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="B871" s="2" t="s">
-        <v>794</v>
+        <v>933</v>
       </c>
       <c r="C871" s="2" t="s">
         <v>694</v>
@@ -17023,21 +17038,21 @@
     </row>
     <row r="872" customHeight="1" spans="1:3">
       <c r="A872" s="2" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="B872" s="2" t="s">
-        <v>1424</v>
+        <v>939</v>
       </c>
       <c r="C872" s="2" t="s">
-        <v>1425</v>
+        <v>694</v>
       </c>
     </row>
     <row r="873" customHeight="1" spans="1:3">
       <c r="A873" s="2" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="B873" s="2" t="s">
-        <v>1427</v>
+        <v>794</v>
       </c>
       <c r="C873" s="2" t="s">
         <v>694</v>
@@ -17045,21 +17060,21 @@
     </row>
     <row r="874" customHeight="1" spans="1:3">
       <c r="A874" s="2" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B874" s="2" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C874" s="2" t="s">
         <v>1428</v>
-      </c>
-      <c r="B874" s="2" t="s">
-        <v>1429</v>
-      </c>
-      <c r="C874" s="2" t="s">
-        <v>970</v>
       </c>
     </row>
     <row r="875" customHeight="1" spans="1:3">
       <c r="A875" s="2" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B875" s="2" t="s">
         <v>1430</v>
-      </c>
-      <c r="B875" s="2" t="s">
-        <v>738</v>
       </c>
       <c r="C875" s="2" t="s">
         <v>694</v>
@@ -17073,7 +17088,7 @@
         <v>1432</v>
       </c>
       <c r="C876" s="2" t="s">
-        <v>694</v>
+        <v>970</v>
       </c>
     </row>
     <row r="877" customHeight="1" spans="1:3">
@@ -17081,7 +17096,7 @@
         <v>1433</v>
       </c>
       <c r="B877" s="2" t="s">
-        <v>749</v>
+        <v>738</v>
       </c>
       <c r="C877" s="2" t="s">
         <v>694</v>
@@ -17092,7 +17107,7 @@
         <v>1434</v>
       </c>
       <c r="B878" s="2" t="s">
-        <v>766</v>
+        <v>1435</v>
       </c>
       <c r="C878" s="2" t="s">
         <v>694</v>
@@ -17100,10 +17115,10 @@
     </row>
     <row r="879" customHeight="1" spans="1:3">
       <c r="A879" s="2" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="B879" s="2" t="s">
-        <v>791</v>
+        <v>749</v>
       </c>
       <c r="C879" s="2" t="s">
         <v>694</v>
@@ -17111,10 +17126,10 @@
     </row>
     <row r="880" customHeight="1" spans="1:3">
       <c r="A880" s="2" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="B880" s="2" t="s">
-        <v>735</v>
+        <v>766</v>
       </c>
       <c r="C880" s="2" t="s">
         <v>694</v>
@@ -17122,10 +17137,10 @@
     </row>
     <row r="881" customHeight="1" spans="1:3">
       <c r="A881" s="2" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="B881" s="2" t="s">
-        <v>1305</v>
+        <v>791</v>
       </c>
       <c r="C881" s="2" t="s">
         <v>694</v>
@@ -17133,10 +17148,10 @@
     </row>
     <row r="882" customHeight="1" spans="1:3">
       <c r="A882" s="2" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="B882" s="2" t="s">
-        <v>791</v>
+        <v>735</v>
       </c>
       <c r="C882" s="2" t="s">
         <v>694</v>
@@ -17144,10 +17159,10 @@
     </row>
     <row r="883" customHeight="1" spans="1:3">
       <c r="A883" s="2" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="B883" s="2" t="s">
-        <v>1440</v>
+        <v>1308</v>
       </c>
       <c r="C883" s="2" t="s">
         <v>694</v>
@@ -17158,7 +17173,7 @@
         <v>1441</v>
       </c>
       <c r="B884" s="2" t="s">
-        <v>836</v>
+        <v>791</v>
       </c>
       <c r="C884" s="2" t="s">
         <v>694</v>
@@ -17169,7 +17184,7 @@
         <v>1442</v>
       </c>
       <c r="B885" s="2" t="s">
-        <v>751</v>
+        <v>1443</v>
       </c>
       <c r="C885" s="2" t="s">
         <v>694</v>
@@ -17177,10 +17192,10 @@
     </row>
     <row r="886" customHeight="1" spans="1:3">
       <c r="A886" s="2" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="B886" s="2" t="s">
-        <v>1444</v>
+        <v>836</v>
       </c>
       <c r="C886" s="2" t="s">
         <v>694</v>
@@ -17191,7 +17206,7 @@
         <v>1445</v>
       </c>
       <c r="B887" s="2" t="s">
-        <v>943</v>
+        <v>751</v>
       </c>
       <c r="C887" s="2" t="s">
         <v>694</v>
@@ -17213,7 +17228,7 @@
         <v>1448</v>
       </c>
       <c r="B889" s="2" t="s">
-        <v>794</v>
+        <v>943</v>
       </c>
       <c r="C889" s="2" t="s">
         <v>694</v>
@@ -17235,7 +17250,7 @@
         <v>1451</v>
       </c>
       <c r="B891" s="2" t="s">
-        <v>1299</v>
+        <v>794</v>
       </c>
       <c r="C891" s="2" t="s">
         <v>694</v>
@@ -17257,7 +17272,7 @@
         <v>1454</v>
       </c>
       <c r="B893" s="2" t="s">
-        <v>979</v>
+        <v>1302</v>
       </c>
       <c r="C893" s="2" t="s">
         <v>694</v>
@@ -17279,7 +17294,7 @@
         <v>1457</v>
       </c>
       <c r="B895" s="2" t="s">
-        <v>1174</v>
+        <v>979</v>
       </c>
       <c r="C895" s="2" t="s">
         <v>694</v>
@@ -17290,7 +17305,7 @@
         <v>1458</v>
       </c>
       <c r="B896" s="2" t="s">
-        <v>735</v>
+        <v>1459</v>
       </c>
       <c r="C896" s="2" t="s">
         <v>694</v>
@@ -17298,10 +17313,10 @@
     </row>
     <row r="897" customHeight="1" spans="1:3">
       <c r="A897" s="2" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="B897" s="2" t="s">
-        <v>1314</v>
+        <v>1175</v>
       </c>
       <c r="C897" s="2" t="s">
         <v>694</v>
@@ -17309,10 +17324,10 @@
     </row>
     <row r="898" customHeight="1" spans="1:3">
       <c r="A898" s="2" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="B898" s="2" t="s">
-        <v>802</v>
+        <v>735</v>
       </c>
       <c r="C898" s="2" t="s">
         <v>694</v>
@@ -17320,10 +17335,10 @@
     </row>
     <row r="899" customHeight="1" spans="1:3">
       <c r="A899" s="2" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="B899" s="2" t="s">
-        <v>1462</v>
+        <v>1317</v>
       </c>
       <c r="C899" s="2" t="s">
         <v>694</v>
@@ -17334,7 +17349,7 @@
         <v>1463</v>
       </c>
       <c r="B900" s="2" t="s">
-        <v>1464</v>
+        <v>802</v>
       </c>
       <c r="C900" s="2" t="s">
         <v>694</v>
@@ -17342,10 +17357,10 @@
     </row>
     <row r="901" customHeight="1" spans="1:3">
       <c r="A901" s="2" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B901" s="2" t="s">
         <v>1465</v>
-      </c>
-      <c r="B901" s="2" t="s">
-        <v>1299</v>
       </c>
       <c r="C901" s="2" t="s">
         <v>694</v>
@@ -17356,7 +17371,7 @@
         <v>1466</v>
       </c>
       <c r="B902" s="2" t="s">
-        <v>1432</v>
+        <v>1467</v>
       </c>
       <c r="C902" s="2" t="s">
         <v>694</v>
@@ -17364,10 +17379,10 @@
     </row>
     <row r="903" customHeight="1" spans="1:3">
       <c r="A903" s="2" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="B903" s="2" t="s">
-        <v>919</v>
+        <v>1302</v>
       </c>
       <c r="C903" s="2" t="s">
         <v>694</v>
@@ -17375,10 +17390,10 @@
     </row>
     <row r="904" customHeight="1" spans="1:3">
       <c r="A904" s="2" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="B904" s="2" t="s">
-        <v>1469</v>
+        <v>1435</v>
       </c>
       <c r="C904" s="2" t="s">
         <v>694</v>
@@ -17389,7 +17404,7 @@
         <v>1470</v>
       </c>
       <c r="B905" s="2" t="s">
-        <v>943</v>
+        <v>919</v>
       </c>
       <c r="C905" s="2" t="s">
         <v>694</v>
@@ -17400,7 +17415,7 @@
         <v>1471</v>
       </c>
       <c r="B906" s="2" t="s">
-        <v>747</v>
+        <v>1472</v>
       </c>
       <c r="C906" s="2" t="s">
         <v>694</v>
@@ -17408,10 +17423,10 @@
     </row>
     <row r="907" customHeight="1" spans="1:3">
       <c r="A907" s="2" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="B907" s="2" t="s">
-        <v>742</v>
+        <v>943</v>
       </c>
       <c r="C907" s="2" t="s">
         <v>694</v>
@@ -17419,10 +17434,10 @@
     </row>
     <row r="908" customHeight="1" spans="1:3">
       <c r="A908" s="2" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="B908" s="2" t="s">
-        <v>1474</v>
+        <v>747</v>
       </c>
       <c r="C908" s="2" t="s">
         <v>694</v>
@@ -17433,7 +17448,7 @@
         <v>1475</v>
       </c>
       <c r="B909" s="2" t="s">
-        <v>1476</v>
+        <v>742</v>
       </c>
       <c r="C909" s="2" t="s">
         <v>694</v>
@@ -17441,10 +17456,10 @@
     </row>
     <row r="910" customHeight="1" spans="1:3">
       <c r="A910" s="2" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B910" s="2" t="s">
         <v>1477</v>
-      </c>
-      <c r="B910" s="2" t="s">
-        <v>1478</v>
       </c>
       <c r="C910" s="2" t="s">
         <v>694</v>
@@ -17452,10 +17467,10 @@
     </row>
     <row r="911" customHeight="1" spans="1:3">
       <c r="A911" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B911" s="2" t="s">
         <v>1479</v>
-      </c>
-      <c r="B911" s="2" t="s">
-        <v>802</v>
       </c>
       <c r="C911" s="2" t="s">
         <v>694</v>
@@ -17466,7 +17481,7 @@
         <v>1480</v>
       </c>
       <c r="B912" s="2" t="s">
-        <v>842</v>
+        <v>1481</v>
       </c>
       <c r="C912" s="2" t="s">
         <v>694</v>
@@ -17474,10 +17489,10 @@
     </row>
     <row r="913" customHeight="1" spans="1:4">
       <c r="A913" s="2" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="B913" s="2" t="s">
-        <v>1482</v>
+        <v>802</v>
       </c>
       <c r="C913" s="2" t="s">
         <v>694</v>
@@ -17488,7 +17503,7 @@
         <v>1483</v>
       </c>
       <c r="B914" s="2" t="s">
-        <v>873</v>
+        <v>842</v>
       </c>
       <c r="C914" s="2" t="s">
         <v>694</v>
@@ -17510,7 +17525,7 @@
         <v>1486</v>
       </c>
       <c r="B916" s="2" t="s">
-        <v>1487</v>
+        <v>873</v>
       </c>
       <c r="C916" s="2" t="s">
         <v>694</v>
@@ -17518,13 +17533,13 @@
     </row>
     <row r="917" customHeight="1" spans="1:4">
       <c r="A917" s="2" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B917" s="2" t="s">
         <v>1488</v>
       </c>
-      <c r="B917" s="2" t="s">
-        <v>969</v>
-      </c>
       <c r="C917" s="2" t="s">
-        <v>970</v>
+        <v>694</v>
       </c>
     </row>
     <row r="918" customHeight="1" spans="1:4">
@@ -17543,18 +17558,18 @@
         <v>1491</v>
       </c>
       <c r="B919" s="2" t="s">
-        <v>1492</v>
+        <v>969</v>
       </c>
       <c r="C919" s="2" t="s">
-        <v>694</v>
+        <v>970</v>
       </c>
     </row>
     <row r="920" customHeight="1" spans="1:4">
       <c r="A920" s="2" t="s">
+        <v>1492</v>
+      </c>
+      <c r="B920" s="2" t="s">
         <v>1493</v>
-      </c>
-      <c r="B920" s="2" t="s">
-        <v>759</v>
       </c>
       <c r="C920" s="2" t="s">
         <v>694</v>
@@ -17565,7 +17580,7 @@
         <v>1494</v>
       </c>
       <c r="B921" s="2" t="s">
-        <v>1299</v>
+        <v>1495</v>
       </c>
       <c r="C921" s="2" t="s">
         <v>694</v>
@@ -17573,66 +17588,66 @@
     </row>
     <row r="922" customHeight="1" spans="1:4">
       <c r="A922" s="2" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="B922" s="2" t="s">
-        <v>1123</v>
+        <v>759</v>
       </c>
       <c r="C922" s="2" t="s">
-        <v>970</v>
+        <v>694</v>
       </c>
     </row>
     <row r="923" customHeight="1" spans="1:4">
       <c r="A923" s="2" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="B923" s="2" t="s">
-        <v>1474</v>
+        <v>1302</v>
       </c>
       <c r="C923" s="2" t="s">
         <v>694</v>
       </c>
     </row>
     <row r="924" customHeight="1" spans="1:4">
-      <c r="A924" s="13" t="s">
-        <v>1497</v>
-      </c>
-      <c r="B924" s="13" t="s">
+      <c r="A924" s="2" t="s">
         <v>1498</v>
       </c>
-      <c r="C924" s="13" t="s">
-        <v>705</v>
-      </c>
-      <c r="D924" s="14"/>
+      <c r="B924" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C924" s="2" t="s">
+        <v>970</v>
+      </c>
     </row>
     <row r="925" customHeight="1" spans="1:4">
       <c r="A925" s="2" t="s">
         <v>1499</v>
       </c>
       <c r="B925" s="2" t="s">
-        <v>794</v>
+        <v>1477</v>
       </c>
       <c r="C925" s="2" t="s">
         <v>694</v>
       </c>
     </row>
     <row r="926" customHeight="1" spans="1:4">
-      <c r="A926" s="2" t="s">
+      <c r="A926" s="13" t="s">
         <v>1500</v>
       </c>
-      <c r="B926" s="2" t="s">
-        <v>1196</v>
-      </c>
-      <c r="C926" s="2" t="s">
-        <v>694</v>
-      </c>
+      <c r="B926" s="13" t="s">
+        <v>1501</v>
+      </c>
+      <c r="C926" s="13" t="s">
+        <v>705</v>
+      </c>
+      <c r="D926" s="14"/>
     </row>
     <row r="927" customHeight="1" spans="1:4">
       <c r="A927" s="2" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B927" s="2" t="s">
-        <v>1432</v>
+        <v>794</v>
       </c>
       <c r="C927" s="2" t="s">
         <v>694</v>
@@ -17640,10 +17655,10 @@
     </row>
     <row r="928" customHeight="1" spans="1:4">
       <c r="A928" s="2" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="B928" s="2" t="s">
-        <v>751</v>
+        <v>1197</v>
       </c>
       <c r="C928" s="2" t="s">
         <v>694</v>
@@ -17651,10 +17666,10 @@
     </row>
     <row r="929" customHeight="1" spans="1:3">
       <c r="A929" s="2" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B929" s="2" t="s">
-        <v>759</v>
+        <v>1435</v>
       </c>
       <c r="C929" s="2" t="s">
         <v>694</v>
@@ -17662,10 +17677,10 @@
     </row>
     <row r="930" customHeight="1" spans="1:3">
       <c r="A930" s="2" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="B930" s="2" t="s">
-        <v>802</v>
+        <v>751</v>
       </c>
       <c r="C930" s="2" t="s">
         <v>694</v>
@@ -17673,21 +17688,21 @@
     </row>
     <row r="931" customHeight="1" spans="1:3">
       <c r="A931" s="2" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="B931" s="2" t="s">
-        <v>1297</v>
+        <v>759</v>
       </c>
       <c r="C931" s="2" t="s">
-        <v>762</v>
+        <v>694</v>
       </c>
     </row>
     <row r="932" customHeight="1" spans="1:3">
       <c r="A932" s="2" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="B932" s="2" t="s">
-        <v>770</v>
+        <v>802</v>
       </c>
       <c r="C932" s="2" t="s">
         <v>694</v>
@@ -17695,13 +17710,13 @@
     </row>
     <row r="933" customHeight="1" spans="1:3">
       <c r="A933" s="2" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="B933" s="2" t="s">
-        <v>1508</v>
+        <v>1300</v>
       </c>
       <c r="C933" s="2" t="s">
-        <v>694</v>
+        <v>762</v>
       </c>
     </row>
     <row r="934" customHeight="1" spans="1:3">
@@ -17753,7 +17768,7 @@
         <v>1515</v>
       </c>
       <c r="B938" s="2" t="s">
-        <v>1516</v>
+        <v>770</v>
       </c>
       <c r="C938" s="2" t="s">
         <v>694</v>
@@ -17761,10 +17776,10 @@
     </row>
     <row r="939" customHeight="1" spans="1:3">
       <c r="A939" s="2" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B939" s="2" t="s">
         <v>1517</v>
-      </c>
-      <c r="B939" s="2" t="s">
-        <v>693</v>
       </c>
       <c r="C939" s="2" t="s">
         <v>694</v>
@@ -17775,7 +17790,7 @@
         <v>1518</v>
       </c>
       <c r="B940" s="2" t="s">
-        <v>723</v>
+        <v>1519</v>
       </c>
       <c r="C940" s="2" t="s">
         <v>694</v>
@@ -17783,10 +17798,10 @@
     </row>
     <row r="941" customHeight="1" spans="1:3">
       <c r="A941" s="2" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="B941" s="2" t="s">
-        <v>1520</v>
+        <v>693</v>
       </c>
       <c r="C941" s="2" t="s">
         <v>694</v>
@@ -17797,7 +17812,7 @@
         <v>1521</v>
       </c>
       <c r="B942" s="2" t="s">
-        <v>881</v>
+        <v>723</v>
       </c>
       <c r="C942" s="2" t="s">
         <v>694</v>
@@ -17808,7 +17823,7 @@
         <v>1522</v>
       </c>
       <c r="B943" s="2" t="s">
-        <v>889</v>
+        <v>1523</v>
       </c>
       <c r="C943" s="2" t="s">
         <v>694</v>
@@ -17816,10 +17831,10 @@
     </row>
     <row r="944" customHeight="1" spans="1:3">
       <c r="A944" s="2" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="B944" s="2" t="s">
-        <v>1524</v>
+        <v>881</v>
       </c>
       <c r="C944" s="2" t="s">
         <v>694</v>
@@ -17830,7 +17845,7 @@
         <v>1525</v>
       </c>
       <c r="B945" s="2" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="C945" s="2" t="s">
         <v>694</v>
@@ -17841,7 +17856,7 @@
         <v>1526</v>
       </c>
       <c r="B946" s="2" t="s">
-        <v>766</v>
+        <v>1527</v>
       </c>
       <c r="C946" s="2" t="s">
         <v>694</v>
@@ -17849,10 +17864,10 @@
     </row>
     <row r="947" customHeight="1" spans="1:3">
       <c r="A947" s="2" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="B947" s="2" t="s">
-        <v>1528</v>
+        <v>892</v>
       </c>
       <c r="C947" s="2" t="s">
         <v>694</v>
@@ -17863,7 +17878,7 @@
         <v>1529</v>
       </c>
       <c r="B948" s="2" t="s">
-        <v>1530</v>
+        <v>766</v>
       </c>
       <c r="C948" s="2" t="s">
         <v>694</v>
@@ -17871,10 +17886,10 @@
     </row>
     <row r="949" customHeight="1" spans="1:3">
       <c r="A949" s="2" t="s">
+        <v>1530</v>
+      </c>
+      <c r="B949" s="2" t="s">
         <v>1531</v>
-      </c>
-      <c r="B949" s="2" t="s">
-        <v>1532</v>
       </c>
       <c r="C949" s="2" t="s">
         <v>694</v>
@@ -17882,10 +17897,10 @@
     </row>
     <row r="950" customHeight="1" spans="1:3">
       <c r="A950" s="2" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B950" s="2" t="s">
         <v>1533</v>
-      </c>
-      <c r="B950" s="2" t="s">
-        <v>974</v>
       </c>
       <c r="C950" s="2" t="s">
         <v>694</v>
@@ -17907,7 +17922,7 @@
         <v>1536</v>
       </c>
       <c r="B952" s="2" t="s">
-        <v>740</v>
+        <v>974</v>
       </c>
       <c r="C952" s="2" t="s">
         <v>694</v>
@@ -17921,7 +17936,7 @@
         <v>1538</v>
       </c>
       <c r="C953" s="2" t="s">
-        <v>762</v>
+        <v>694</v>
       </c>
     </row>
     <row r="954" customHeight="1" spans="1:3">
@@ -17929,7 +17944,7 @@
         <v>1539</v>
       </c>
       <c r="B954" s="2" t="s">
-        <v>1540</v>
+        <v>740</v>
       </c>
       <c r="C954" s="2" t="s">
         <v>694</v>
@@ -17937,13 +17952,13 @@
     </row>
     <row r="955" customHeight="1" spans="1:3">
       <c r="A955" s="2" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B955" s="2" t="s">
         <v>1541</v>
       </c>
-      <c r="B955" s="2" t="s">
-        <v>1084</v>
-      </c>
       <c r="C955" s="2" t="s">
-        <v>694</v>
+        <v>762</v>
       </c>
     </row>
     <row r="956" customHeight="1" spans="1:3">
@@ -17951,7 +17966,7 @@
         <v>1542</v>
       </c>
       <c r="B956" s="2" t="s">
-        <v>1482</v>
+        <v>1543</v>
       </c>
       <c r="C956" s="2" t="s">
         <v>694</v>
@@ -17959,10 +17974,10 @@
     </row>
     <row r="957" customHeight="1" spans="1:3">
       <c r="A957" s="2" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="B957" s="2" t="s">
-        <v>1544</v>
+        <v>1084</v>
       </c>
       <c r="C957" s="2" t="s">
         <v>694</v>
@@ -17973,7 +17988,7 @@
         <v>1545</v>
       </c>
       <c r="B958" s="2" t="s">
-        <v>1546</v>
+        <v>1485</v>
       </c>
       <c r="C958" s="2" t="s">
         <v>694</v>
@@ -17981,10 +17996,10 @@
     </row>
     <row r="959" customHeight="1" spans="1:3">
       <c r="A959" s="2" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B959" s="2" t="s">
         <v>1547</v>
-      </c>
-      <c r="B959" s="2" t="s">
-        <v>919</v>
       </c>
       <c r="C959" s="2" t="s">
         <v>694</v>
@@ -18006,7 +18021,7 @@
         <v>1550</v>
       </c>
       <c r="B961" s="2" t="s">
-        <v>974</v>
+        <v>919</v>
       </c>
       <c r="C961" s="2" t="s">
         <v>694</v>
@@ -18017,7 +18032,7 @@
         <v>1551</v>
       </c>
       <c r="B962" s="2" t="s">
-        <v>910</v>
+        <v>1552</v>
       </c>
       <c r="C962" s="2" t="s">
         <v>694</v>
@@ -18025,10 +18040,10 @@
     </row>
     <row r="963" customHeight="1" spans="1:4">
       <c r="A963" s="2" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="B963" s="2" t="s">
-        <v>766</v>
+        <v>974</v>
       </c>
       <c r="C963" s="2" t="s">
         <v>694</v>
@@ -18036,10 +18051,10 @@
     </row>
     <row r="964" customHeight="1" spans="1:4">
       <c r="A964" s="2" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="B964" s="2" t="s">
-        <v>862</v>
+        <v>910</v>
       </c>
       <c r="C964" s="2" t="s">
         <v>694</v>
@@ -18047,56 +18062,55 @@
     </row>
     <row r="965" customHeight="1" spans="1:4">
       <c r="A965" s="2" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="B965" s="2" t="s">
-        <v>974</v>
+        <v>766</v>
       </c>
       <c r="C965" s="2" t="s">
         <v>694</v>
       </c>
     </row>
     <row r="966" customHeight="1" spans="1:4">
-      <c r="A966" s="13" t="s">
-        <v>1555</v>
-      </c>
-      <c r="B966" s="13" t="s">
-        <v>735</v>
-      </c>
-      <c r="C966" s="13" t="s">
-        <v>736</v>
-      </c>
-      <c r="D966" s="14"/>
+      <c r="A966" s="2" t="s">
+        <v>1556</v>
+      </c>
+      <c r="B966" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="C966" s="2" t="s">
+        <v>694</v>
+      </c>
     </row>
     <row r="967" customHeight="1" spans="1:4">
       <c r="A967" s="2" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="B967" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="C967" s="2" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="968" customHeight="1" spans="1:4">
+      <c r="A968" s="13" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B968" s="13" t="s">
         <v>735</v>
       </c>
-      <c r="C967" s="2" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="968" customHeight="1" spans="1:4">
-      <c r="A968" s="2" t="s">
-        <v>1557</v>
-      </c>
-      <c r="B968" s="2" t="s">
-        <v>1558</v>
-      </c>
-      <c r="C968" s="2" t="s">
-        <v>694</v>
-      </c>
-      <c r="D968" s="2"/>
+      <c r="C968" s="13" t="s">
+        <v>736</v>
+      </c>
+      <c r="D968" s="14"/>
     </row>
     <row r="969" customHeight="1" spans="1:4">
-      <c r="A969" s="1">
-        <v>1219</v>
+      <c r="A969" s="2" t="s">
+        <v>1559</v>
       </c>
       <c r="B969" s="2" t="s">
-        <v>1559</v>
+        <v>735</v>
       </c>
       <c r="C969" s="2" t="s">
         <v>694</v>
@@ -18107,18 +18121,19 @@
         <v>1560</v>
       </c>
       <c r="B970" s="2" t="s">
-        <v>768</v>
+        <v>1561</v>
       </c>
       <c r="C970" s="2" t="s">
         <v>694</v>
       </c>
+      <c r="D970" s="2"/>
     </row>
     <row r="971" customHeight="1" spans="1:4">
-      <c r="A971" s="2" t="s">
-        <v>1561</v>
+      <c r="A971" s="1">
+        <v>1219</v>
       </c>
       <c r="B971" s="2" t="s">
-        <v>747</v>
+        <v>1562</v>
       </c>
       <c r="C971" s="2" t="s">
         <v>694</v>
@@ -18126,10 +18141,10 @@
     </row>
     <row r="972" customHeight="1" spans="1:4">
       <c r="A972" s="2" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B972" s="2" t="s">
-        <v>876</v>
+        <v>768</v>
       </c>
       <c r="C972" s="2" t="s">
         <v>694</v>
@@ -18137,46 +18152,46 @@
     </row>
     <row r="973" customHeight="1" spans="1:4">
       <c r="A973" s="2" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="B973" s="2" t="s">
-        <v>848</v>
+        <v>747</v>
       </c>
       <c r="C973" s="2" t="s">
-        <v>762</v>
+        <v>694</v>
       </c>
     </row>
     <row r="974" customHeight="1" spans="1:4">
       <c r="A974" s="2" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="B974" s="2" t="s">
-        <v>860</v>
+        <v>876</v>
       </c>
       <c r="C974" s="2" t="s">
-        <v>762</v>
+        <v>694</v>
       </c>
     </row>
     <row r="975" customHeight="1" spans="1:4">
       <c r="A975" s="2" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="B975" s="2" t="s">
-        <v>1099</v>
+        <v>848</v>
       </c>
       <c r="C975" s="2" t="s">
-        <v>694</v>
+        <v>762</v>
       </c>
     </row>
     <row r="976" customHeight="1" spans="1:4">
       <c r="A976" s="2" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B976" s="2" t="s">
-        <v>1567</v>
+        <v>860</v>
       </c>
       <c r="C976" s="2" t="s">
-        <v>694</v>
+        <v>762</v>
       </c>
     </row>
     <row r="977" customHeight="1" spans="1:3">
@@ -18184,7 +18199,7 @@
         <v>1568</v>
       </c>
       <c r="B977" s="2" t="s">
-        <v>1569</v>
+        <v>1099</v>
       </c>
       <c r="C977" s="2" t="s">
         <v>694</v>
@@ -18192,10 +18207,10 @@
     </row>
     <row r="978" customHeight="1" spans="1:3">
       <c r="A978" s="2" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B978" s="2" t="s">
         <v>1570</v>
-      </c>
-      <c r="B978" s="2" t="s">
-        <v>1571</v>
       </c>
       <c r="C978" s="2" t="s">
         <v>694</v>
@@ -18203,10 +18218,10 @@
     </row>
     <row r="979" customHeight="1" spans="1:3">
       <c r="A979" s="2" t="s">
+        <v>1571</v>
+      </c>
+      <c r="B979" s="2" t="s">
         <v>1572</v>
-      </c>
-      <c r="B979" s="2" t="s">
-        <v>838</v>
       </c>
       <c r="C979" s="2" t="s">
         <v>694</v>
@@ -18217,7 +18232,7 @@
         <v>1573</v>
       </c>
       <c r="B980" s="2" t="s">
-        <v>768</v>
+        <v>1574</v>
       </c>
       <c r="C980" s="2" t="s">
         <v>694</v>
@@ -18225,10 +18240,10 @@
     </row>
     <row r="981" customHeight="1" spans="1:3">
       <c r="A981" s="2" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="B981" s="2" t="s">
-        <v>1574</v>
+        <v>838</v>
       </c>
       <c r="C981" s="2" t="s">
         <v>694</v>
@@ -18236,10 +18251,10 @@
     </row>
     <row r="982" customHeight="1" spans="1:3">
       <c r="A982" s="2" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B982" s="2" t="s">
-        <v>751</v>
+        <v>768</v>
       </c>
       <c r="C982" s="2" t="s">
         <v>694</v>
@@ -18261,14 +18276,14 @@
         <v>1578</v>
       </c>
       <c r="B984" s="2" t="s">
-        <v>709</v>
+        <v>751</v>
       </c>
       <c r="C984" s="2" t="s">
         <v>694</v>
       </c>
     </row>
     <row r="985" customHeight="1" spans="1:3">
-      <c r="A985" s="25" t="s">
+      <c r="A985" s="2" t="s">
         <v>1579</v>
       </c>
       <c r="B985" s="2" t="s">
@@ -18283,18 +18298,18 @@
         <v>1581</v>
       </c>
       <c r="B986" s="2" t="s">
-        <v>740</v>
+        <v>709</v>
       </c>
       <c r="C986" s="2" t="s">
         <v>694</v>
       </c>
     </row>
     <row r="987" customHeight="1" spans="1:3">
-      <c r="A987" s="2" t="s">
+      <c r="A987" s="25" t="s">
         <v>1582</v>
       </c>
       <c r="B987" s="2" t="s">
-        <v>713</v>
+        <v>1583</v>
       </c>
       <c r="C987" s="2" t="s">
         <v>694</v>
@@ -18302,10 +18317,10 @@
     </row>
     <row r="988" customHeight="1" spans="1:3">
       <c r="A988" s="2" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="B988" s="2" t="s">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="C988" s="2" t="s">
         <v>694</v>
@@ -18313,10 +18328,10 @@
     </row>
     <row r="989" customHeight="1" spans="1:3">
       <c r="A989" s="2" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="B989" s="2" t="s">
-        <v>791</v>
+        <v>713</v>
       </c>
       <c r="C989" s="2" t="s">
         <v>694</v>
@@ -18324,10 +18339,10 @@
     </row>
     <row r="990" customHeight="1" spans="1:3">
       <c r="A990" s="2" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="B990" s="2" t="s">
-        <v>1585</v>
+        <v>735</v>
       </c>
       <c r="C990" s="2" t="s">
         <v>694</v>
@@ -18338,7 +18353,7 @@
         <v>1586</v>
       </c>
       <c r="B991" s="2" t="s">
-        <v>766</v>
+        <v>791</v>
       </c>
       <c r="C991" s="2" t="s">
         <v>694</v>
@@ -18349,7 +18364,7 @@
         <v>1587</v>
       </c>
       <c r="B992" s="2" t="s">
-        <v>791</v>
+        <v>1588</v>
       </c>
       <c r="C992" s="2" t="s">
         <v>694</v>
@@ -18357,10 +18372,10 @@
     </row>
     <row r="993" customHeight="1" spans="1:3">
       <c r="A993" s="2" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="B993" s="2" t="s">
-        <v>889</v>
+        <v>766</v>
       </c>
       <c r="C993" s="2" t="s">
         <v>694</v>
@@ -18368,10 +18383,10 @@
     </row>
     <row r="994" customHeight="1" spans="1:3">
       <c r="A994" s="2" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="B994" s="2" t="s">
-        <v>1590</v>
+        <v>791</v>
       </c>
       <c r="C994" s="2" t="s">
         <v>694</v>
@@ -18382,7 +18397,7 @@
         <v>1591</v>
       </c>
       <c r="B995" s="2" t="s">
-        <v>1592</v>
+        <v>889</v>
       </c>
       <c r="C995" s="2" t="s">
         <v>694</v>
@@ -18390,10 +18405,10 @@
     </row>
     <row r="996" customHeight="1" spans="1:3">
       <c r="A996" s="2" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B996" s="2" t="s">
         <v>1593</v>
-      </c>
-      <c r="B996" s="2" t="s">
-        <v>1592</v>
       </c>
       <c r="C996" s="2" t="s">
         <v>694</v>
@@ -18404,7 +18419,7 @@
         <v>1594</v>
       </c>
       <c r="B997" s="2" t="s">
-        <v>1293</v>
+        <v>1595</v>
       </c>
       <c r="C997" s="2" t="s">
         <v>694</v>
@@ -18412,10 +18427,10 @@
     </row>
     <row r="998" customHeight="1" spans="1:3">
       <c r="A998" s="2" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B998" s="2" t="s">
         <v>1595</v>
-      </c>
-      <c r="B998" s="2" t="s">
-        <v>1046</v>
       </c>
       <c r="C998" s="2" t="s">
         <v>694</v>
@@ -18423,10 +18438,10 @@
     </row>
     <row r="999" customHeight="1" spans="1:3">
       <c r="A999" s="2" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="B999" s="2" t="s">
-        <v>1597</v>
+        <v>1296</v>
       </c>
       <c r="C999" s="2" t="s">
         <v>694</v>
@@ -18437,7 +18452,7 @@
         <v>1598</v>
       </c>
       <c r="B1000" s="2" t="s">
-        <v>919</v>
+        <v>1046</v>
       </c>
       <c r="C1000" s="2" t="s">
         <v>694</v>
@@ -18459,7 +18474,7 @@
         <v>1601</v>
       </c>
       <c r="B1002" s="2" t="s">
-        <v>1602</v>
+        <v>919</v>
       </c>
       <c r="C1002" s="2" t="s">
         <v>694</v>
@@ -18467,10 +18482,10 @@
     </row>
     <row r="1003" customHeight="1" spans="1:3">
       <c r="A1003" s="2" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B1003" s="2" t="s">
         <v>1603</v>
-      </c>
-      <c r="B1003" s="2" t="s">
-        <v>738</v>
       </c>
       <c r="C1003" s="2" t="s">
         <v>694</v>
@@ -18481,7 +18496,7 @@
         <v>1604</v>
       </c>
       <c r="B1004" s="2" t="s">
-        <v>738</v>
+        <v>1605</v>
       </c>
       <c r="C1004" s="2" t="s">
         <v>694</v>
@@ -18489,10 +18504,10 @@
     </row>
     <row r="1005" customHeight="1" spans="1:3">
       <c r="A1005" s="2" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="B1005" s="2" t="s">
-        <v>800</v>
+        <v>738</v>
       </c>
       <c r="C1005" s="2" t="s">
         <v>694</v>
@@ -18500,10 +18515,10 @@
     </row>
     <row r="1006" customHeight="1" spans="1:3">
       <c r="A1006" s="2" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="B1006" s="2" t="s">
-        <v>1607</v>
+        <v>738</v>
       </c>
       <c r="C1006" s="2" t="s">
         <v>694</v>
@@ -18514,7 +18529,7 @@
         <v>1608</v>
       </c>
       <c r="B1007" s="2" t="s">
-        <v>791</v>
+        <v>800</v>
       </c>
       <c r="C1007" s="2" t="s">
         <v>694</v>
@@ -18525,18 +18540,18 @@
         <v>1609</v>
       </c>
       <c r="B1008" s="2" t="s">
-        <v>800</v>
+        <v>1610</v>
       </c>
       <c r="C1008" s="2" t="s">
-        <v>762</v>
+        <v>694</v>
       </c>
     </row>
     <row r="1009" customHeight="1" spans="1:3">
       <c r="A1009" s="2" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="B1009" s="2" t="s">
-        <v>742</v>
+        <v>791</v>
       </c>
       <c r="C1009" s="2" t="s">
         <v>694</v>
@@ -18544,21 +18559,21 @@
     </row>
     <row r="1010" customHeight="1" spans="1:3">
       <c r="A1010" s="2" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="B1010" s="2" t="s">
-        <v>698</v>
+        <v>800</v>
       </c>
       <c r="C1010" s="2" t="s">
-        <v>694</v>
+        <v>762</v>
       </c>
     </row>
     <row r="1011" customHeight="1" spans="1:3">
       <c r="A1011" s="2" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="B1011" s="2" t="s">
-        <v>999</v>
+        <v>742</v>
       </c>
       <c r="C1011" s="2" t="s">
         <v>694</v>
@@ -18566,10 +18581,10 @@
     </row>
     <row r="1012" customHeight="1" spans="1:3">
       <c r="A1012" s="2" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="B1012" s="2" t="s">
-        <v>1196</v>
+        <v>698</v>
       </c>
       <c r="C1012" s="2" t="s">
         <v>694</v>
@@ -18577,10 +18592,10 @@
     </row>
     <row r="1013" customHeight="1" spans="1:3">
       <c r="A1013" s="2" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="B1013" s="2" t="s">
-        <v>791</v>
+        <v>999</v>
       </c>
       <c r="C1013" s="2" t="s">
         <v>694</v>
@@ -18588,13 +18603,13 @@
     </row>
     <row r="1014" customHeight="1" spans="1:3">
       <c r="A1014" s="2" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="B1014" s="2" t="s">
-        <v>1616</v>
+        <v>1197</v>
       </c>
       <c r="C1014" s="2" t="s">
-        <v>970</v>
+        <v>694</v>
       </c>
     </row>
     <row r="1015" customHeight="1" spans="1:3">
@@ -18602,7 +18617,7 @@
         <v>1617</v>
       </c>
       <c r="B1015" s="2" t="s">
-        <v>988</v>
+        <v>791</v>
       </c>
       <c r="C1015" s="2" t="s">
         <v>694</v>
@@ -18613,18 +18628,18 @@
         <v>1618</v>
       </c>
       <c r="B1016" s="2" t="s">
-        <v>698</v>
+        <v>1619</v>
       </c>
       <c r="C1016" s="2" t="s">
-        <v>694</v>
+        <v>970</v>
       </c>
     </row>
     <row r="1017" customHeight="1" spans="1:3">
       <c r="A1017" s="2" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="B1017" s="2" t="s">
-        <v>717</v>
+        <v>988</v>
       </c>
       <c r="C1017" s="2" t="s">
         <v>694</v>
@@ -18632,10 +18647,10 @@
     </row>
     <row r="1018" customHeight="1" spans="1:3">
       <c r="A1018" s="2" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="B1018" s="2" t="s">
-        <v>1132</v>
+        <v>698</v>
       </c>
       <c r="C1018" s="2" t="s">
         <v>694</v>
@@ -18643,21 +18658,21 @@
     </row>
     <row r="1019" customHeight="1" spans="1:3">
       <c r="A1019" s="2" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="B1019" s="2" t="s">
-        <v>954</v>
+        <v>717</v>
       </c>
       <c r="C1019" s="2" t="s">
-        <v>762</v>
+        <v>694</v>
       </c>
     </row>
     <row r="1020" customHeight="1" spans="1:3">
       <c r="A1020" s="2" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="B1020" s="2" t="s">
-        <v>1299</v>
+        <v>1133</v>
       </c>
       <c r="C1020" s="2" t="s">
         <v>694</v>
@@ -18665,21 +18680,21 @@
     </row>
     <row r="1021" customHeight="1" spans="1:3">
       <c r="A1021" s="2" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="B1021" s="2" t="s">
-        <v>1116</v>
+        <v>954</v>
       </c>
       <c r="C1021" s="2" t="s">
-        <v>694</v>
+        <v>762</v>
       </c>
     </row>
     <row r="1022" customHeight="1" spans="1:3">
       <c r="A1022" s="2" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="B1022" s="2" t="s">
-        <v>717</v>
+        <v>1302</v>
       </c>
       <c r="C1022" s="2" t="s">
         <v>694</v>
@@ -18687,10 +18702,10 @@
     </row>
     <row r="1023" customHeight="1" spans="1:3">
       <c r="A1023" s="2" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="B1023" s="2" t="s">
-        <v>919</v>
+        <v>1117</v>
       </c>
       <c r="C1023" s="2" t="s">
         <v>694</v>
@@ -18698,10 +18713,10 @@
     </row>
     <row r="1024" customHeight="1" spans="1:3">
       <c r="A1024" s="2" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="B1024" s="2" t="s">
-        <v>791</v>
+        <v>717</v>
       </c>
       <c r="C1024" s="2" t="s">
         <v>694</v>
@@ -18709,21 +18724,21 @@
     </row>
     <row r="1025" customHeight="1" spans="1:3">
       <c r="A1025" s="2" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="B1025" s="2" t="s">
-        <v>1123</v>
+        <v>919</v>
       </c>
       <c r="C1025" s="2" t="s">
-        <v>970</v>
+        <v>694</v>
       </c>
     </row>
     <row r="1026" customHeight="1" spans="1:3">
       <c r="A1026" s="2" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="B1026" s="2" t="s">
-        <v>1629</v>
+        <v>791</v>
       </c>
       <c r="C1026" s="2" t="s">
         <v>694</v>
@@ -18734,10 +18749,10 @@
         <v>1630</v>
       </c>
       <c r="B1027" s="2" t="s">
-        <v>1462</v>
+        <v>1124</v>
       </c>
       <c r="C1027" s="2" t="s">
-        <v>694</v>
+        <v>970</v>
       </c>
     </row>
     <row r="1028" customHeight="1" spans="1:3">
@@ -18745,7 +18760,7 @@
         <v>1631</v>
       </c>
       <c r="B1028" s="2" t="s">
-        <v>751</v>
+        <v>1632</v>
       </c>
       <c r="C1028" s="2" t="s">
         <v>694</v>
@@ -18753,10 +18768,10 @@
     </row>
     <row r="1029" customHeight="1" spans="1:3">
       <c r="A1029" s="2" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="B1029" s="2" t="s">
-        <v>766</v>
+        <v>1465</v>
       </c>
       <c r="C1029" s="2" t="s">
         <v>694</v>
@@ -18764,10 +18779,10 @@
     </row>
     <row r="1030" customHeight="1" spans="1:3">
       <c r="A1030" s="2" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="B1030" s="2" t="s">
-        <v>974</v>
+        <v>751</v>
       </c>
       <c r="C1030" s="2" t="s">
         <v>694</v>
@@ -18775,10 +18790,10 @@
     </row>
     <row r="1031" customHeight="1" spans="1:3">
       <c r="A1031" s="2" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="B1031" s="2" t="s">
-        <v>1144</v>
+        <v>766</v>
       </c>
       <c r="C1031" s="2" t="s">
         <v>694</v>
@@ -18786,10 +18801,10 @@
     </row>
     <row r="1032" customHeight="1" spans="1:3">
       <c r="A1032" s="2" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="B1032" s="2" t="s">
-        <v>766</v>
+        <v>974</v>
       </c>
       <c r="C1032" s="2" t="s">
         <v>694</v>
@@ -18797,10 +18812,10 @@
     </row>
     <row r="1033" customHeight="1" spans="1:3">
       <c r="A1033" s="2" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="B1033" s="2" t="s">
-        <v>698</v>
+        <v>1145</v>
       </c>
       <c r="C1033" s="2" t="s">
         <v>694</v>
@@ -18808,10 +18823,10 @@
     </row>
     <row r="1034" customHeight="1" spans="1:3">
       <c r="A1034" s="2" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="B1034" s="2" t="s">
-        <v>1546</v>
+        <v>766</v>
       </c>
       <c r="C1034" s="2" t="s">
         <v>694</v>
@@ -18819,10 +18834,10 @@
     </row>
     <row r="1035" customHeight="1" spans="1:3">
       <c r="A1035" s="2" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="B1035" s="2" t="s">
-        <v>964</v>
+        <v>698</v>
       </c>
       <c r="C1035" s="2" t="s">
         <v>694</v>
@@ -18830,10 +18845,10 @@
     </row>
     <row r="1036" customHeight="1" spans="1:3">
       <c r="A1036" s="2" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="B1036" s="2" t="s">
-        <v>1190</v>
+        <v>1549</v>
       </c>
       <c r="C1036" s="2" t="s">
         <v>694</v>
@@ -18841,10 +18856,10 @@
     </row>
     <row r="1037" customHeight="1" spans="1:3">
       <c r="A1037" s="2" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="B1037" s="2" t="s">
-        <v>945</v>
+        <v>964</v>
       </c>
       <c r="C1037" s="2" t="s">
         <v>694</v>
@@ -18852,10 +18867,10 @@
     </row>
     <row r="1038" customHeight="1" spans="1:3">
       <c r="A1038" s="2" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="B1038" s="2" t="s">
-        <v>910</v>
+        <v>1191</v>
       </c>
       <c r="C1038" s="2" t="s">
         <v>694</v>
@@ -18863,10 +18878,10 @@
     </row>
     <row r="1039" customHeight="1" spans="1:3">
       <c r="A1039" s="2" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="B1039" s="2" t="s">
-        <v>867</v>
+        <v>945</v>
       </c>
       <c r="C1039" s="2" t="s">
         <v>694</v>
@@ -18874,10 +18889,10 @@
     </row>
     <row r="1040" customHeight="1" spans="1:3">
       <c r="A1040" s="2" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B1040" s="2" t="s">
-        <v>735</v>
+        <v>910</v>
       </c>
       <c r="C1040" s="2" t="s">
         <v>694</v>
@@ -18885,10 +18900,10 @@
     </row>
     <row r="1041" customHeight="1" spans="1:3">
       <c r="A1041" s="2" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="B1041" s="2" t="s">
-        <v>709</v>
+        <v>867</v>
       </c>
       <c r="C1041" s="2" t="s">
         <v>694</v>
@@ -18896,10 +18911,10 @@
     </row>
     <row r="1042" customHeight="1" spans="1:3">
       <c r="A1042" s="2" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="B1042" s="2" t="s">
-        <v>887</v>
+        <v>735</v>
       </c>
       <c r="C1042" s="2" t="s">
         <v>694</v>
@@ -18907,10 +18922,10 @@
     </row>
     <row r="1043" customHeight="1" spans="1:3">
       <c r="A1043" s="2" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="B1043" s="2" t="s">
-        <v>804</v>
+        <v>709</v>
       </c>
       <c r="C1043" s="2" t="s">
         <v>694</v>
@@ -18918,10 +18933,10 @@
     </row>
     <row r="1044" customHeight="1" spans="1:3">
       <c r="A1044" s="2" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="B1044" s="2" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="C1044" s="2" t="s">
         <v>694</v>
@@ -18929,21 +18944,21 @@
     </row>
     <row r="1045" customHeight="1" spans="1:3">
       <c r="A1045" s="2" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="B1045" s="2" t="s">
-        <v>1123</v>
+        <v>804</v>
       </c>
       <c r="C1045" s="2" t="s">
-        <v>970</v>
+        <v>694</v>
       </c>
     </row>
     <row r="1046" customHeight="1" spans="1:3">
       <c r="A1046" s="2" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="B1046" s="2" t="s">
-        <v>1111</v>
+        <v>889</v>
       </c>
       <c r="C1046" s="2" t="s">
         <v>694</v>
@@ -18951,21 +18966,21 @@
     </row>
     <row r="1047" customHeight="1" spans="1:3">
       <c r="A1047" s="2" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="B1047" s="2" t="s">
-        <v>876</v>
+        <v>1124</v>
       </c>
       <c r="C1047" s="2" t="s">
-        <v>694</v>
+        <v>970</v>
       </c>
     </row>
     <row r="1048" customHeight="1" spans="1:3">
       <c r="A1048" s="2" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="B1048" s="2" t="s">
-        <v>1046</v>
+        <v>1111</v>
       </c>
       <c r="C1048" s="2" t="s">
         <v>694</v>
@@ -18973,10 +18988,10 @@
     </row>
     <row r="1049" customHeight="1" spans="1:3">
       <c r="A1049" s="2" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="B1049" s="2" t="s">
-        <v>1482</v>
+        <v>876</v>
       </c>
       <c r="C1049" s="2" t="s">
         <v>694</v>
@@ -18984,10 +18999,10 @@
     </row>
     <row r="1050" customHeight="1" spans="1:3">
       <c r="A1050" s="2" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="B1050" s="2" t="s">
-        <v>1654</v>
+        <v>1046</v>
       </c>
       <c r="C1050" s="2" t="s">
         <v>694</v>
@@ -18998,7 +19013,7 @@
         <v>1655</v>
       </c>
       <c r="B1051" s="2" t="s">
-        <v>974</v>
+        <v>1485</v>
       </c>
       <c r="C1051" s="2" t="s">
         <v>694</v>
@@ -19009,7 +19024,7 @@
         <v>1656</v>
       </c>
       <c r="B1052" s="2" t="s">
-        <v>735</v>
+        <v>1657</v>
       </c>
       <c r="C1052" s="2" t="s">
         <v>694</v>
@@ -19017,10 +19032,10 @@
     </row>
     <row r="1053" customHeight="1" spans="1:3">
       <c r="A1053" s="2" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="B1053" s="2" t="s">
-        <v>919</v>
+        <v>974</v>
       </c>
       <c r="C1053" s="2" t="s">
         <v>694</v>
@@ -19028,10 +19043,10 @@
     </row>
     <row r="1054" customHeight="1" spans="1:3">
       <c r="A1054" s="2" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="B1054" s="2" t="s">
-        <v>919</v>
+        <v>735</v>
       </c>
       <c r="C1054" s="2" t="s">
         <v>694</v>
@@ -19039,10 +19054,10 @@
     </row>
     <row r="1055" customHeight="1" spans="1:3">
       <c r="A1055" s="2" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="B1055" s="2" t="s">
-        <v>802</v>
+        <v>919</v>
       </c>
       <c r="C1055" s="2" t="s">
         <v>694</v>
@@ -19050,10 +19065,10 @@
     </row>
     <row r="1056" customHeight="1" spans="1:3">
       <c r="A1056" s="2" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="B1056" s="2" t="s">
-        <v>717</v>
+        <v>919</v>
       </c>
       <c r="C1056" s="2" t="s">
         <v>694</v>
@@ -19061,10 +19076,10 @@
     </row>
     <row r="1057" customHeight="1" spans="1:4">
       <c r="A1057" s="2" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="B1057" s="2" t="s">
-        <v>939</v>
+        <v>802</v>
       </c>
       <c r="C1057" s="2" t="s">
         <v>694</v>
@@ -19072,10 +19087,10 @@
     </row>
     <row r="1058" customHeight="1" spans="1:4">
       <c r="A1058" s="2" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="B1058" s="2" t="s">
-        <v>751</v>
+        <v>717</v>
       </c>
       <c r="C1058" s="2" t="s">
         <v>694</v>
@@ -19083,10 +19098,10 @@
     </row>
     <row r="1059" customHeight="1" spans="1:4">
       <c r="A1059" s="2" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="B1059" s="2" t="s">
-        <v>1664</v>
+        <v>939</v>
       </c>
       <c r="C1059" s="2" t="s">
         <v>694</v>
@@ -19097,7 +19112,7 @@
         <v>1665</v>
       </c>
       <c r="B1060" s="2" t="s">
-        <v>1666</v>
+        <v>751</v>
       </c>
       <c r="C1060" s="2" t="s">
         <v>694</v>
@@ -19105,10 +19120,10 @@
     </row>
     <row r="1061" customHeight="1" spans="1:4">
       <c r="A1061" s="2" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B1061" s="2" t="s">
         <v>1667</v>
-      </c>
-      <c r="B1061" s="2" t="s">
-        <v>1668</v>
       </c>
       <c r="C1061" s="2" t="s">
         <v>694</v>
@@ -19116,10 +19131,10 @@
     </row>
     <row r="1062" customHeight="1" spans="1:4">
       <c r="A1062" s="2" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B1062" s="2" t="s">
         <v>1669</v>
-      </c>
-      <c r="B1062" s="2" t="s">
-        <v>802</v>
       </c>
       <c r="C1062" s="2" t="s">
         <v>694</v>
@@ -19130,7 +19145,7 @@
         <v>1670</v>
       </c>
       <c r="B1063" s="2" t="s">
-        <v>1535</v>
+        <v>1671</v>
       </c>
       <c r="C1063" s="2" t="s">
         <v>694</v>
@@ -19138,13 +19153,13 @@
     </row>
     <row r="1064" customHeight="1" spans="1:4">
       <c r="A1064" s="2" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="B1064" s="2" t="s">
-        <v>1672</v>
+        <v>802</v>
       </c>
       <c r="C1064" s="2" t="s">
-        <v>762</v>
+        <v>694</v>
       </c>
     </row>
     <row r="1065" customHeight="1" spans="1:4">
@@ -19152,7 +19167,7 @@
         <v>1673</v>
       </c>
       <c r="B1065" s="2" t="s">
-        <v>709</v>
+        <v>1538</v>
       </c>
       <c r="C1065" s="2" t="s">
         <v>694</v>
@@ -19166,61 +19181,61 @@
         <v>1675</v>
       </c>
       <c r="C1066" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="1067" customHeight="1" spans="1:4">
+      <c r="A1067" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="B1067" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="C1067" s="2" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="1068" customHeight="1" spans="1:4">
+      <c r="A1068" s="2" t="s">
+        <v>1677</v>
+      </c>
+      <c r="B1068" s="2" t="s">
+        <v>1678</v>
+      </c>
+      <c r="C1068" s="2" t="s">
         <v>970</v>
       </c>
     </row>
-    <row r="1067" customHeight="1" spans="1:4">
-      <c r="A1067" s="13" t="s">
-        <v>1676</v>
-      </c>
-      <c r="B1067" s="13" t="s">
-        <v>1677</v>
-      </c>
-      <c r="C1067" s="13" t="s">
+    <row r="1069" customHeight="1" spans="1:4">
+      <c r="A1069" s="13" t="s">
+        <v>1679</v>
+      </c>
+      <c r="B1069" s="13" t="s">
+        <v>1680</v>
+      </c>
+      <c r="C1069" s="13" t="s">
         <v>702</v>
       </c>
-      <c r="D1067" s="14"/>
-    </row>
-    <row r="1068" customHeight="1" spans="1:4">
-      <c r="A1068" s="13" t="s">
-        <v>1678</v>
-      </c>
-      <c r="B1068" s="13" t="s">
-        <v>1679</v>
-      </c>
-      <c r="C1068" s="13" t="s">
+      <c r="D1069" s="14"/>
+    </row>
+    <row r="1070" customHeight="1" spans="1:4">
+      <c r="A1070" s="13" t="s">
+        <v>1681</v>
+      </c>
+      <c r="B1070" s="13" t="s">
+        <v>1682</v>
+      </c>
+      <c r="C1070" s="13" t="s">
         <v>705</v>
       </c>
-      <c r="D1068" s="14"/>
-    </row>
-    <row r="1069" customHeight="1" spans="1:4">
-      <c r="A1069" s="1" t="s">
-        <v>1680</v>
-      </c>
-      <c r="B1069" s="2" t="s">
-        <v>1681</v>
-      </c>
-      <c r="C1069" s="2" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="1070" customHeight="1" spans="1:4">
-      <c r="A1070" s="2" t="s">
-        <v>1682</v>
-      </c>
-      <c r="B1070" s="2" t="s">
-        <v>887</v>
-      </c>
-      <c r="C1070" s="2" t="s">
-        <v>694</v>
-      </c>
+      <c r="D1070" s="14"/>
     </row>
     <row r="1071" customHeight="1" spans="1:4">
-      <c r="A1071" s="2" t="s">
+      <c r="A1071" s="1" t="s">
         <v>1683</v>
       </c>
       <c r="B1071" s="2" t="s">
-        <v>770</v>
+        <v>1684</v>
       </c>
       <c r="C1071" s="2" t="s">
         <v>694</v>
@@ -19228,10 +19243,10 @@
     </row>
     <row r="1072" customHeight="1" spans="1:4">
       <c r="A1072" s="2" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="B1072" s="2" t="s">
-        <v>698</v>
+        <v>887</v>
       </c>
       <c r="C1072" s="2" t="s">
         <v>694</v>
@@ -19239,10 +19254,10 @@
     </row>
     <row r="1073" customHeight="1" spans="1:4">
       <c r="A1073" s="2" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="B1073" s="2" t="s">
-        <v>887</v>
+        <v>770</v>
       </c>
       <c r="C1073" s="2" t="s">
         <v>694</v>
@@ -19250,10 +19265,10 @@
     </row>
     <row r="1074" customHeight="1" spans="1:4">
       <c r="A1074" s="2" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="B1074" s="2" t="s">
-        <v>802</v>
+        <v>698</v>
       </c>
       <c r="C1074" s="2" t="s">
         <v>694</v>
@@ -19261,10 +19276,10 @@
     </row>
     <row r="1075" customHeight="1" spans="1:4">
       <c r="A1075" s="2" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="B1075" s="2" t="s">
-        <v>1299</v>
+        <v>887</v>
       </c>
       <c r="C1075" s="2" t="s">
         <v>694</v>
@@ -19272,10 +19287,10 @@
     </row>
     <row r="1076" customHeight="1" spans="1:4">
       <c r="A1076" s="2" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="B1076" s="2" t="s">
-        <v>1689</v>
+        <v>802</v>
       </c>
       <c r="C1076" s="2" t="s">
         <v>694</v>
@@ -19286,7 +19301,7 @@
         <v>1690</v>
       </c>
       <c r="B1077" s="2" t="s">
-        <v>1691</v>
+        <v>1302</v>
       </c>
       <c r="C1077" s="2" t="s">
         <v>694</v>
@@ -19294,10 +19309,10 @@
     </row>
     <row r="1078" customHeight="1" spans="1:4">
       <c r="A1078" s="2" t="s">
+        <v>1691</v>
+      </c>
+      <c r="B1078" s="2" t="s">
         <v>1692</v>
-      </c>
-      <c r="B1078" s="2" t="s">
-        <v>919</v>
       </c>
       <c r="C1078" s="2" t="s">
         <v>694</v>
@@ -19308,7 +19323,7 @@
         <v>1693</v>
       </c>
       <c r="B1079" s="2" t="s">
-        <v>1462</v>
+        <v>1694</v>
       </c>
       <c r="C1079" s="2" t="s">
         <v>694</v>
@@ -19316,10 +19331,10 @@
     </row>
     <row r="1080" customHeight="1" spans="1:4">
       <c r="A1080" s="2" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="B1080" s="2" t="s">
-        <v>1511</v>
+        <v>919</v>
       </c>
       <c r="C1080" s="2" t="s">
         <v>694</v>
@@ -19327,10 +19342,10 @@
     </row>
     <row r="1081" customHeight="1" spans="1:4">
       <c r="A1081" s="2" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="B1081" s="2" t="s">
-        <v>1696</v>
+        <v>1465</v>
       </c>
       <c r="C1081" s="2" t="s">
         <v>694</v>
@@ -19341,7 +19356,7 @@
         <v>1697</v>
       </c>
       <c r="B1082" s="2" t="s">
-        <v>751</v>
+        <v>1514</v>
       </c>
       <c r="C1082" s="2" t="s">
         <v>694</v>
@@ -19352,7 +19367,7 @@
         <v>1698</v>
       </c>
       <c r="B1083" s="2" t="s">
-        <v>693</v>
+        <v>1699</v>
       </c>
       <c r="C1083" s="2" t="s">
         <v>694</v>
@@ -19360,58 +19375,58 @@
     </row>
     <row r="1084" customHeight="1" spans="1:4">
       <c r="A1084" s="2" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B1084" s="2" t="s">
-        <v>831</v>
+        <v>751</v>
       </c>
       <c r="C1084" s="2" t="s">
         <v>694</v>
       </c>
     </row>
     <row r="1085" customHeight="1" spans="1:4">
-      <c r="A1085" s="13" t="s">
-        <v>1700</v>
-      </c>
-      <c r="B1085" s="13" t="s">
-        <v>860</v>
-      </c>
-      <c r="C1085" s="13" t="s">
-        <v>851</v>
-      </c>
-      <c r="D1085" s="14"/>
+      <c r="A1085" s="2" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B1085" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="C1085" s="2" t="s">
+        <v>694</v>
+      </c>
     </row>
     <row r="1086" customHeight="1" spans="1:4">
       <c r="A1086" s="2" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="B1086" s="2" t="s">
-        <v>693</v>
+        <v>831</v>
       </c>
       <c r="C1086" s="2" t="s">
-        <v>1702</v>
+        <v>694</v>
       </c>
     </row>
     <row r="1087" customHeight="1" spans="1:4">
-      <c r="A1087" s="2" t="s">
+      <c r="A1087" s="13" t="s">
         <v>1703</v>
       </c>
-      <c r="B1087" s="2" t="s">
-        <v>1704</v>
-      </c>
-      <c r="C1087" s="2" t="s">
-        <v>1702</v>
-      </c>
+      <c r="B1087" s="13" t="s">
+        <v>860</v>
+      </c>
+      <c r="C1087" s="13" t="s">
+        <v>851</v>
+      </c>
+      <c r="D1087" s="14"/>
     </row>
     <row r="1088" customHeight="1" spans="1:4">
       <c r="A1088" s="2" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B1088" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="C1088" s="2" t="s">
         <v>1705</v>
-      </c>
-      <c r="B1088" s="2" t="s">
-        <v>867</v>
-      </c>
-      <c r="C1088" s="2" t="s">
-        <v>1702</v>
       </c>
     </row>
     <row r="1089" customHeight="1" spans="1:3">
@@ -19422,7 +19437,7 @@
         <v>1707</v>
       </c>
       <c r="C1089" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1090" customHeight="1" spans="1:3">
@@ -19430,21 +19445,21 @@
         <v>1708</v>
       </c>
       <c r="B1090" s="2" t="s">
-        <v>1709</v>
+        <v>867</v>
       </c>
       <c r="C1090" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1091" customHeight="1" spans="1:3">
       <c r="A1091" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="B1091" s="2" t="s">
         <v>1710</v>
       </c>
-      <c r="B1091" s="2" t="s">
-        <v>1709</v>
-      </c>
       <c r="C1091" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1092" customHeight="1" spans="1:3">
@@ -19452,21 +19467,21 @@
         <v>1711</v>
       </c>
       <c r="B1092" s="2" t="s">
-        <v>1709</v>
+        <v>1712</v>
       </c>
       <c r="C1092" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1093" customHeight="1" spans="1:3">
       <c r="A1093" s="2" t="s">
+        <v>1713</v>
+      </c>
+      <c r="B1093" s="2" t="s">
         <v>1712</v>
       </c>
-      <c r="B1093" s="2" t="s">
-        <v>1713</v>
-      </c>
       <c r="C1093" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1094" customHeight="1" spans="1:3">
@@ -19474,10 +19489,10 @@
         <v>1714</v>
       </c>
       <c r="B1094" s="2" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="C1094" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1095" customHeight="1" spans="1:3">
@@ -19485,21 +19500,21 @@
         <v>1715</v>
       </c>
       <c r="B1095" s="2" t="s">
-        <v>1713</v>
+        <v>1716</v>
       </c>
       <c r="C1095" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1096" customHeight="1" spans="1:3">
       <c r="A1096" s="2" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B1096" s="2" t="s">
         <v>1716</v>
       </c>
-      <c r="B1096" s="2" t="s">
-        <v>1717</v>
-      </c>
       <c r="C1096" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1097" customHeight="1" spans="1:3">
@@ -19507,10 +19522,10 @@
         <v>1718</v>
       </c>
       <c r="B1097" s="2" t="s">
-        <v>999</v>
+        <v>1716</v>
       </c>
       <c r="C1097" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1098" customHeight="1" spans="1:3">
@@ -19518,21 +19533,21 @@
         <v>1719</v>
       </c>
       <c r="B1098" s="2" t="s">
-        <v>999</v>
+        <v>1720</v>
       </c>
       <c r="C1098" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1099" customHeight="1" spans="1:3">
       <c r="A1099" s="2" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="B1099" s="2" t="s">
-        <v>1721</v>
+        <v>999</v>
       </c>
       <c r="C1099" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1100" customHeight="1" spans="1:3">
@@ -19540,10 +19555,10 @@
         <v>1722</v>
       </c>
       <c r="B1100" s="2" t="s">
-        <v>1721</v>
+        <v>999</v>
       </c>
       <c r="C1100" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1101" customHeight="1" spans="1:3">
@@ -19551,186 +19566,186 @@
         <v>1723</v>
       </c>
       <c r="B1101" s="2" t="s">
-        <v>1721</v>
+        <v>1724</v>
       </c>
       <c r="C1101" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1102" customHeight="1" spans="1:3">
       <c r="A1102" s="2" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B1102" s="2" t="s">
         <v>1724</v>
       </c>
-      <c r="B1102" s="2" t="s">
-        <v>1721</v>
-      </c>
       <c r="C1102" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1103" customHeight="1" spans="1:3">
       <c r="A1103" s="2" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="B1103" s="2" t="s">
-        <v>1721</v>
+        <v>1724</v>
       </c>
       <c r="C1103" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1104" customHeight="1" spans="1:3">
       <c r="A1104" s="2" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="B1104" s="2" t="s">
-        <v>1721</v>
+        <v>1724</v>
       </c>
       <c r="C1104" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1105" customHeight="1" spans="1:3">
       <c r="A1105" s="2" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="B1105" s="2" t="s">
-        <v>873</v>
+        <v>1724</v>
       </c>
       <c r="C1105" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1106" customHeight="1" spans="1:3">
       <c r="A1106" s="2" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="B1106" s="2" t="s">
-        <v>873</v>
+        <v>1724</v>
       </c>
       <c r="C1106" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1107" customHeight="1" spans="1:3">
       <c r="A1107" s="2" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="B1107" s="2" t="s">
         <v>873</v>
       </c>
       <c r="C1107" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1108" customHeight="1" spans="1:3">
       <c r="A1108" s="2" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="B1108" s="2" t="s">
         <v>873</v>
       </c>
       <c r="C1108" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1109" customHeight="1" spans="1:3">
       <c r="A1109" s="2" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="B1109" s="2" t="s">
         <v>873</v>
       </c>
       <c r="C1109" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1110" customHeight="1" spans="1:3">
       <c r="A1110" s="2" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="B1110" s="2" t="s">
         <v>873</v>
       </c>
       <c r="C1110" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1111" customHeight="1" spans="1:3">
       <c r="A1111" s="2" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="B1111" s="2" t="s">
         <v>873</v>
       </c>
       <c r="C1111" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1112" customHeight="1" spans="1:3">
       <c r="A1112" s="2" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="B1112" s="2" t="s">
         <v>873</v>
       </c>
       <c r="C1112" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1113" customHeight="1" spans="1:3">
       <c r="A1113" s="2" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="B1113" s="2" t="s">
         <v>873</v>
       </c>
       <c r="C1113" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1114" customHeight="1" spans="1:3">
       <c r="A1114" s="2" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="B1114" s="2" t="s">
         <v>873</v>
       </c>
       <c r="C1114" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1115" customHeight="1" spans="1:3">
       <c r="A1115" s="2" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="B1115" s="2" t="s">
         <v>873</v>
       </c>
       <c r="C1115" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1116" customHeight="1" spans="1:3">
       <c r="A1116" s="2" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="B1116" s="2" t="s">
         <v>873</v>
       </c>
       <c r="C1116" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1117" customHeight="1" spans="1:3">
       <c r="A1117" s="2" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="B1117" s="2" t="s">
-        <v>1740</v>
+        <v>873</v>
       </c>
       <c r="C1117" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1118" customHeight="1" spans="1:3">
@@ -19738,21 +19753,21 @@
         <v>1741</v>
       </c>
       <c r="B1118" s="2" t="s">
-        <v>1742</v>
+        <v>873</v>
       </c>
       <c r="C1118" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1119" customHeight="1" spans="1:3">
       <c r="A1119" s="2" t="s">
+        <v>1742</v>
+      </c>
+      <c r="B1119" s="2" t="s">
         <v>1743</v>
       </c>
-      <c r="B1119" s="2" t="s">
-        <v>1742</v>
-      </c>
       <c r="C1119" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1120" customHeight="1" spans="1:3">
@@ -19763,7 +19778,7 @@
         <v>1745</v>
       </c>
       <c r="C1120" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1121" customHeight="1" spans="1:4">
@@ -19771,21 +19786,21 @@
         <v>1746</v>
       </c>
       <c r="B1121" s="2" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="C1121" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1122" customHeight="1" spans="1:4">
       <c r="A1122" s="2" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B1122" s="2" t="s">
         <v>1748</v>
       </c>
-      <c r="B1122" s="2" t="s">
-        <v>1747</v>
-      </c>
       <c r="C1122" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1123" customHeight="1" spans="1:4">
@@ -19793,68 +19808,66 @@
         <v>1749</v>
       </c>
       <c r="B1123" s="2" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
       <c r="C1123" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1124" customHeight="1" spans="1:4">
       <c r="A1124" s="2" t="s">
+        <v>1751</v>
+      </c>
+      <c r="B1124" s="2" t="s">
         <v>1750</v>
       </c>
-      <c r="B1124" s="2" t="s">
-        <v>1747</v>
-      </c>
       <c r="C1124" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1125" customHeight="1" spans="1:4">
       <c r="A1125" s="2" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="B1125" s="2" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
       <c r="C1125" s="2" t="s">
-        <v>1702</v>
-      </c>
-      <c r="D1125" s="2"/>
+        <v>1705</v>
+      </c>
     </row>
     <row r="1126" customHeight="1" spans="1:4">
       <c r="A1126" s="2" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B1126" s="2" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
       <c r="C1126" s="2" t="s">
-        <v>1702</v>
-      </c>
-      <c r="D1126" s="2"/>
+        <v>1705</v>
+      </c>
     </row>
     <row r="1127" customHeight="1" spans="1:4">
       <c r="A1127" s="2" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="B1127" s="2" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
       <c r="C1127" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
       <c r="D1127" s="2"/>
     </row>
     <row r="1128" customHeight="1" spans="1:4">
       <c r="A1128" s="2" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="B1128" s="2" t="s">
-        <v>1755</v>
+        <v>1750</v>
       </c>
       <c r="C1128" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
       <c r="D1128" s="2"/>
     </row>
@@ -19863,10 +19876,10 @@
         <v>1756</v>
       </c>
       <c r="B1129" s="2" t="s">
-        <v>1654</v>
+        <v>1750</v>
       </c>
       <c r="C1129" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
       <c r="D1129" s="2"/>
     </row>
@@ -19875,43 +19888,45 @@
         <v>1757</v>
       </c>
       <c r="B1130" s="2" t="s">
-        <v>1654</v>
+        <v>1758</v>
       </c>
       <c r="C1130" s="2" t="s">
-        <v>1702</v>
-      </c>
+        <v>1705</v>
+      </c>
+      <c r="D1130" s="2"/>
     </row>
     <row r="1131" customHeight="1" spans="1:4">
       <c r="A1131" s="2" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="B1131" s="2" t="s">
-        <v>1654</v>
+        <v>1657</v>
       </c>
       <c r="C1131" s="2" t="s">
-        <v>1702</v>
-      </c>
+        <v>1705</v>
+      </c>
+      <c r="D1131" s="2"/>
     </row>
     <row r="1132" customHeight="1" spans="1:4">
       <c r="A1132" s="2" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="B1132" s="2" t="s">
-        <v>1654</v>
+        <v>1657</v>
       </c>
       <c r="C1132" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1133" customHeight="1" spans="1:4">
       <c r="A1133" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B1133" s="2" t="s">
-        <v>1761</v>
+        <v>1657</v>
       </c>
       <c r="C1133" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1134" customHeight="1" spans="1:4">
@@ -19919,10 +19934,10 @@
         <v>1762</v>
       </c>
       <c r="B1134" s="2" t="s">
-        <v>1462</v>
+        <v>1657</v>
       </c>
       <c r="C1134" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1135" customHeight="1" spans="1:4">
@@ -19933,7 +19948,7 @@
         <v>1764</v>
       </c>
       <c r="C1135" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1136" customHeight="1" spans="1:4">
@@ -19941,10 +19956,10 @@
         <v>1765</v>
       </c>
       <c r="B1136" s="2" t="s">
-        <v>1764</v>
+        <v>1465</v>
       </c>
       <c r="C1136" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1137" customHeight="1" spans="1:4">
@@ -19952,43 +19967,43 @@
         <v>1766</v>
       </c>
       <c r="B1137" s="2" t="s">
-        <v>1764</v>
+        <v>1767</v>
       </c>
       <c r="C1137" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1138" customHeight="1" spans="1:4">
       <c r="A1138" s="2" t="s">
+        <v>1768</v>
+      </c>
+      <c r="B1138" s="2" t="s">
         <v>1767</v>
       </c>
-      <c r="B1138" s="2" t="s">
-        <v>802</v>
-      </c>
       <c r="C1138" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1139" customHeight="1" spans="1:4">
       <c r="A1139" s="2" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="B1139" s="2" t="s">
-        <v>802</v>
+        <v>1767</v>
       </c>
       <c r="C1139" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1140" customHeight="1" spans="1:4">
       <c r="A1140" s="2" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="B1140" s="2" t="s">
-        <v>1770</v>
+        <v>802</v>
       </c>
       <c r="C1140" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1141" customHeight="1" spans="1:4">
@@ -19996,79 +20011,79 @@
         <v>1771</v>
       </c>
       <c r="B1141" s="2" t="s">
-        <v>1772</v>
+        <v>802</v>
       </c>
       <c r="C1141" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1142" customHeight="1" spans="1:4">
       <c r="A1142" s="2" t="s">
+        <v>1772</v>
+      </c>
+      <c r="B1142" s="2" t="s">
         <v>1773</v>
       </c>
-      <c r="B1142" s="2" t="s">
-        <v>1774</v>
-      </c>
       <c r="C1142" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1143" customHeight="1" spans="1:4">
       <c r="A1143" s="2" t="s">
+        <v>1774</v>
+      </c>
+      <c r="B1143" s="2" t="s">
         <v>1775</v>
       </c>
-      <c r="B1143" s="2" t="s">
-        <v>1776</v>
-      </c>
       <c r="C1143" s="2" t="s">
-        <v>1702</v>
-      </c>
-      <c r="D1143" s="2" t="s">
-        <v>1777</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1144" customHeight="1" spans="1:4">
       <c r="A1144" s="2" t="s">
-        <v>1778</v>
+        <v>1776</v>
       </c>
       <c r="B1144" s="2" t="s">
-        <v>1779</v>
+        <v>1777</v>
       </c>
       <c r="C1144" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1145" customHeight="1" spans="1:4">
       <c r="A1145" s="2" t="s">
+        <v>1778</v>
+      </c>
+      <c r="B1145" s="2" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C1145" s="2" t="s">
+        <v>1705</v>
+      </c>
+      <c r="D1145" s="2" t="s">
         <v>1780</v>
-      </c>
-      <c r="B1145" s="2" t="s">
-        <v>1781</v>
-      </c>
-      <c r="C1145" s="2" t="s">
-        <v>1702</v>
       </c>
     </row>
     <row r="1146" customHeight="1" spans="1:4">
       <c r="A1146" s="2" t="s">
+        <v>1781</v>
+      </c>
+      <c r="B1146" s="2" t="s">
         <v>1782</v>
       </c>
-      <c r="B1146" s="2" t="s">
-        <v>1783</v>
-      </c>
       <c r="C1146" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1147" customHeight="1" spans="1:4">
       <c r="A1147" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="B1147" s="2" t="s">
         <v>1784</v>
       </c>
-      <c r="B1147" s="2" t="s">
-        <v>1783</v>
-      </c>
       <c r="C1147" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1148" customHeight="1" spans="1:4">
@@ -20076,32 +20091,32 @@
         <v>1785</v>
       </c>
       <c r="B1148" s="2" t="s">
-        <v>1783</v>
+        <v>1786</v>
       </c>
       <c r="C1148" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1149" customHeight="1" spans="1:4">
       <c r="A1149" s="2" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B1149" s="2" t="s">
         <v>1786</v>
       </c>
-      <c r="B1149" s="2" t="s">
-        <v>1783</v>
-      </c>
       <c r="C1149" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1150" customHeight="1" spans="1:4">
       <c r="A1150" s="2" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="B1150" s="2" t="s">
-        <v>1788</v>
+        <v>1786</v>
       </c>
       <c r="C1150" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1151" customHeight="1" spans="1:4">
@@ -20109,21 +20124,21 @@
         <v>1789</v>
       </c>
       <c r="B1151" s="2" t="s">
-        <v>1790</v>
+        <v>1786</v>
       </c>
       <c r="C1151" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1152" customHeight="1" spans="1:4">
       <c r="A1152" s="2" t="s">
+        <v>1790</v>
+      </c>
+      <c r="B1152" s="2" t="s">
         <v>1791</v>
       </c>
-      <c r="B1152" s="2" t="s">
-        <v>1790</v>
-      </c>
       <c r="C1152" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1153" customHeight="1" spans="1:4">
@@ -20131,32 +20146,32 @@
         <v>1792</v>
       </c>
       <c r="B1153" s="2" t="s">
-        <v>1790</v>
+        <v>1793</v>
       </c>
       <c r="C1153" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1154" customHeight="1" spans="1:4">
       <c r="A1154" s="2" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B1154" s="2" t="s">
         <v>1793</v>
       </c>
-      <c r="B1154" s="2" t="s">
-        <v>1664</v>
-      </c>
       <c r="C1154" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1155" customHeight="1" spans="1:4">
       <c r="A1155" s="2" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="B1155" s="2" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="C1155" s="2" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1156" customHeight="1" spans="1:4">
@@ -20164,124 +20179,125 @@
         <v>1796</v>
       </c>
       <c r="B1156" s="2" t="s">
-        <v>1797</v>
+        <v>1667</v>
       </c>
       <c r="C1156" s="2" t="s">
-        <v>1702</v>
-      </c>
-      <c r="D1156" s="2" t="s">
-        <v>1798</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1157" customHeight="1" spans="1:4">
       <c r="A1157" s="2" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
       <c r="B1157" s="2" t="s">
-        <v>1800</v>
+        <v>1798</v>
       </c>
       <c r="C1157" s="2" t="s">
-        <v>1286</v>
-      </c>
-      <c r="D1157" s="2"/>
+        <v>1705</v>
+      </c>
     </row>
     <row r="1158" customHeight="1" spans="1:4">
       <c r="A1158" s="2" t="s">
-        <v>1801</v>
+        <v>1799</v>
       </c>
       <c r="B1158" s="2" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="C1158" s="2" t="s">
-        <v>1286</v>
-      </c>
+        <v>1705</v>
+      </c>
+      <c r="D1158" s="2"/>
     </row>
     <row r="1159" customHeight="1" spans="1:4">
       <c r="A1159" s="2" t="s">
+        <v>1801</v>
+      </c>
+      <c r="B1159" s="2" t="s">
+        <v>1802</v>
+      </c>
+      <c r="C1159" s="2" t="s">
+        <v>1705</v>
+      </c>
+      <c r="D1159" s="2" t="s">
         <v>1803</v>
-      </c>
-      <c r="B1159" s="2" t="s">
-        <v>1804</v>
-      </c>
-      <c r="C1159" s="2" t="s">
-        <v>1286</v>
       </c>
     </row>
     <row r="1160" customHeight="1" spans="1:4">
       <c r="A1160" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="B1160" s="2" t="s">
         <v>1805</v>
       </c>
-      <c r="B1160" s="2" t="s">
-        <v>1806</v>
-      </c>
       <c r="C1160" s="2" t="s">
-        <v>1286</v>
-      </c>
+        <v>1289</v>
+      </c>
+      <c r="D1160" s="2"/>
     </row>
     <row r="1161" customHeight="1" spans="1:4">
       <c r="A1161" s="2" t="s">
+        <v>1806</v>
+      </c>
+      <c r="B1161" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="B1161" s="2" t="s">
-        <v>1808</v>
-      </c>
       <c r="C1161" s="2" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="1162" customHeight="1" spans="1:4">
       <c r="A1162" s="2" t="s">
+        <v>1808</v>
+      </c>
+      <c r="B1162" s="2" t="s">
         <v>1809</v>
       </c>
-      <c r="B1162" s="2" t="s">
-        <v>1810</v>
-      </c>
       <c r="C1162" s="2" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="1163" customHeight="1" spans="1:4">
       <c r="A1163" s="2" t="s">
+        <v>1810</v>
+      </c>
+      <c r="B1163" s="2" t="s">
         <v>1811</v>
       </c>
-      <c r="B1163" s="2" t="s">
-        <v>1812</v>
-      </c>
       <c r="C1163" s="2" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="1164" customHeight="1" spans="1:4">
       <c r="A1164" s="2" t="s">
+        <v>1812</v>
+      </c>
+      <c r="B1164" s="2" t="s">
         <v>1813</v>
       </c>
-      <c r="B1164" s="2" t="s">
-        <v>1814</v>
-      </c>
       <c r="C1164" s="2" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="1165" customHeight="1" spans="1:4">
       <c r="A1165" s="2" t="s">
+        <v>1814</v>
+      </c>
+      <c r="B1165" s="2" t="s">
         <v>1815</v>
       </c>
-      <c r="B1165" s="2" t="s">
-        <v>1816</v>
-      </c>
       <c r="C1165" s="2" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="1166" customHeight="1" spans="1:4">
       <c r="A1166" s="2" t="s">
+        <v>1816</v>
+      </c>
+      <c r="B1166" s="2" t="s">
         <v>1817</v>
       </c>
-      <c r="B1166" s="2" t="s">
-        <v>979</v>
-      </c>
       <c r="C1166" s="2" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="1167" customHeight="1" spans="1:4">
@@ -20289,154 +20305,156 @@
         <v>1818</v>
       </c>
       <c r="B1167" s="2" t="s">
-        <v>1808</v>
+        <v>1819</v>
       </c>
       <c r="C1167" s="2" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="1168" customHeight="1" spans="1:4">
       <c r="A1168" s="2" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="B1168" s="2" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="C1168" s="2" t="s">
-        <v>1286</v>
-      </c>
-    </row>
-    <row r="1169" customHeight="1" spans="1:4">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="1169" customHeight="1" spans="1:3">
       <c r="A1169" s="2" t="s">
+        <v>1822</v>
+      </c>
+      <c r="B1169" s="2" t="s">
+        <v>979</v>
+      </c>
+      <c r="C1169" s="2" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="1170" customHeight="1" spans="1:3">
+      <c r="A1170" s="2" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B1170" s="2" t="s">
+        <v>1813</v>
+      </c>
+      <c r="C1170" s="2" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="1171" customHeight="1" spans="1:3">
+      <c r="A1171" s="2" t="s">
+        <v>1824</v>
+      </c>
+      <c r="B1171" s="2" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C1171" s="2" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="1172" customHeight="1" spans="1:3">
+      <c r="A1172" s="2" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1172" s="2" t="s">
+        <v>1809</v>
+      </c>
+      <c r="C1172" s="2" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="1173" customHeight="1" spans="1:3">
+      <c r="A1173" s="2" t="s">
+        <v>1827</v>
+      </c>
+      <c r="B1173" s="2" t="s">
+        <v>1813</v>
+      </c>
+      <c r="C1173" s="2" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="1174" customHeight="1" spans="1:3">
+      <c r="A1174" s="2" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B1174" s="2" t="s">
         <v>1821</v>
       </c>
-      <c r="B1169" s="2" t="s">
-        <v>1804</v>
-      </c>
-      <c r="C1169" s="2" t="s">
-        <v>1286</v>
-      </c>
-    </row>
-    <row r="1170" customHeight="1" spans="1:4">
-      <c r="A1170" s="2" t="s">
-        <v>1822</v>
-      </c>
-      <c r="B1170" s="2" t="s">
-        <v>1808</v>
-      </c>
-      <c r="C1170" s="2" t="s">
-        <v>1286</v>
-      </c>
-    </row>
-    <row r="1171" customHeight="1" spans="1:4">
-      <c r="A1171" s="2" t="s">
-        <v>1823</v>
-      </c>
-      <c r="B1171" s="2" t="s">
-        <v>1816</v>
-      </c>
-      <c r="C1171" s="2" t="s">
-        <v>1286</v>
-      </c>
-    </row>
-    <row r="1172" customHeight="1" spans="1:4">
-      <c r="A1172" s="2" t="s">
-        <v>1824</v>
-      </c>
-      <c r="B1172" s="2" t="s">
-        <v>1812</v>
-      </c>
-      <c r="C1172" s="2" t="s">
-        <v>1286</v>
-      </c>
-    </row>
-    <row r="1173" customHeight="1" spans="1:4">
-      <c r="A1173" s="2" t="s">
-        <v>1825</v>
-      </c>
-      <c r="B1173" s="2" t="s">
-        <v>1808</v>
-      </c>
-      <c r="C1173" s="2" t="s">
-        <v>1286</v>
-      </c>
-    </row>
-    <row r="1174" customHeight="1" spans="1:4">
-      <c r="A1174" s="2" t="s">
-        <v>1826</v>
-      </c>
-      <c r="B1174" s="2" t="s">
-        <v>1827</v>
-      </c>
       <c r="C1174" s="2" t="s">
-        <v>1286</v>
-      </c>
-    </row>
-    <row r="1175" customHeight="1" spans="1:4">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="1175" customHeight="1" spans="1:3">
       <c r="A1175" s="2" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="B1175" s="2" t="s">
-        <v>1808</v>
+        <v>1817</v>
       </c>
       <c r="C1175" s="2" t="s">
-        <v>1286</v>
-      </c>
-    </row>
-    <row r="1176" customHeight="1" spans="1:4">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="1176" customHeight="1" spans="1:3">
       <c r="A1176" s="2" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="B1176" s="2" t="s">
-        <v>1808</v>
+        <v>1813</v>
       </c>
       <c r="C1176" s="2" t="s">
-        <v>1286</v>
-      </c>
-    </row>
-    <row r="1177" customHeight="1" spans="1:4">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="1177" customHeight="1" spans="1:3">
       <c r="A1177" s="2" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="B1177" s="2" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="C1177" s="2" t="s">
-        <v>1286</v>
-      </c>
-    </row>
-    <row r="1178" customHeight="1" spans="1:4">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="1178" customHeight="1" spans="1:3">
       <c r="A1178" s="2" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="B1178" s="2" t="s">
-        <v>1833</v>
+        <v>1813</v>
       </c>
       <c r="C1178" s="2" t="s">
-        <v>1286</v>
-      </c>
-    </row>
-    <row r="1179" customHeight="1" spans="1:4">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="1179" customHeight="1" spans="1:3">
       <c r="A1179" s="2" t="s">
         <v>1834</v>
       </c>
       <c r="B1179" s="2" t="s">
+        <v>1813</v>
+      </c>
+      <c r="C1179" s="2" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="1180" customHeight="1" spans="1:3">
+      <c r="A1180" s="2" t="s">
         <v>1835</v>
       </c>
-      <c r="C1179" s="2" t="s">
-        <v>1286</v>
-      </c>
-    </row>
-    <row r="1180" customHeight="1" spans="1:4">
-      <c r="A1180" s="2" t="s">
+      <c r="B1180" s="2" t="s">
         <v>1836</v>
       </c>
-      <c r="B1180" s="2"/>
       <c r="C1180" s="2" t="s">
-        <v>1286</v>
-      </c>
-    </row>
-    <row r="1181" customHeight="1" spans="1:4">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="1181" customHeight="1" spans="1:3">
       <c r="A1181" s="2" t="s">
         <v>1837</v>
       </c>
@@ -20444,212 +20462,243 @@
         <v>1838</v>
       </c>
       <c r="C1181" s="2" t="s">
-        <v>1286</v>
-      </c>
-    </row>
-    <row r="1182" customHeight="1" spans="1:4">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="1182" customHeight="1" spans="1:3">
       <c r="A1182" s="2" t="s">
         <v>1839</v>
       </c>
-      <c r="B1182" s="9" t="s">
+      <c r="B1182" s="2" t="s">
         <v>1840</v>
       </c>
       <c r="C1182" s="2" t="s">
-        <v>1286</v>
-      </c>
-      <c r="D1182" s="2"/>
-    </row>
-    <row r="1183" customHeight="1" spans="1:4">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="1183" customHeight="1" spans="1:3">
       <c r="A1183" s="2" t="s">
         <v>1841</v>
       </c>
-      <c r="B1183" s="9" t="s">
+      <c r="B1183" s="2"/>
+      <c r="C1183" s="2" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="1184" customHeight="1" spans="1:3">
+      <c r="A1184" s="2" t="s">
         <v>1842</v>
       </c>
-      <c r="C1183" s="2" t="s">
-        <v>1286</v>
-      </c>
-      <c r="D1183" s="2"/>
-    </row>
-    <row r="1184" customHeight="1" spans="1:4">
-      <c r="A1184" s="2" t="s">
+      <c r="B1184" s="2" t="s">
         <v>1843</v>
       </c>
-      <c r="B1184" s="9" t="s">
-        <v>1844</v>
-      </c>
       <c r="C1184" s="2" t="s">
-        <v>1286</v>
-      </c>
-      <c r="D1184" s="2"/>
+        <v>1289</v>
+      </c>
     </row>
     <row r="1185" customHeight="1" spans="1:4">
       <c r="A1185" s="2" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B1185" s="9" t="s">
         <v>1845</v>
       </c>
-      <c r="B1185" s="9" t="s">
-        <v>1846</v>
-      </c>
       <c r="C1185" s="2" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="D1185" s="2"/>
     </row>
     <row r="1186" customHeight="1" spans="1:4">
       <c r="A1186" s="2" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B1186" s="9" t="s">
         <v>1847</v>
       </c>
-      <c r="B1186" s="2" t="s">
-        <v>1848</v>
-      </c>
       <c r="C1186" s="2" t="s">
-        <v>1286</v>
-      </c>
+        <v>1289</v>
+      </c>
+      <c r="D1186" s="2"/>
     </row>
     <row r="1187" customHeight="1" spans="1:4">
       <c r="A1187" s="2" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B1187" s="9" t="s">
         <v>1849</v>
       </c>
-      <c r="B1187" s="2" t="s">
-        <v>1808</v>
-      </c>
       <c r="C1187" s="2" t="s">
-        <v>1286</v>
-      </c>
+        <v>1289</v>
+      </c>
+      <c r="D1187" s="2"/>
     </row>
     <row r="1188" customHeight="1" spans="1:4">
       <c r="A1188" s="2" t="s">
         <v>1850</v>
       </c>
-      <c r="B1188" s="2" t="s">
-        <v>1808</v>
+      <c r="B1188" s="9" t="s">
+        <v>1851</v>
       </c>
       <c r="C1188" s="2" t="s">
-        <v>1286</v>
-      </c>
+        <v>1289</v>
+      </c>
+      <c r="D1188" s="2"/>
     </row>
     <row r="1189" customHeight="1" spans="1:4">
       <c r="A1189" s="2" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="B1189" s="2" t="s">
-        <v>1827</v>
+        <v>1853</v>
       </c>
       <c r="C1189" s="2" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="1190" customHeight="1" spans="1:4">
       <c r="A1190" s="2" t="s">
-        <v>1852</v>
+        <v>1854</v>
       </c>
       <c r="B1190" s="2" t="s">
-        <v>1853</v>
+        <v>1813</v>
       </c>
       <c r="C1190" s="2" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="1191" customHeight="1" spans="1:4">
       <c r="A1191" s="2" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="B1191" s="2" t="s">
-        <v>1816</v>
+        <v>1813</v>
       </c>
       <c r="C1191" s="2" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="1192" customHeight="1" spans="1:4">
       <c r="A1192" s="2" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="B1192" s="2" t="s">
-        <v>1808</v>
+        <v>1832</v>
       </c>
       <c r="C1192" s="2" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="1193" customHeight="1" spans="1:4">
       <c r="A1193" s="2" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B1193" s="9" t="s">
         <v>1857</v>
       </c>
+      <c r="B1193" s="2" t="s">
+        <v>1858</v>
+      </c>
       <c r="C1193" s="2" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="1194" customHeight="1" spans="1:4">
       <c r="A1194" s="2" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="B1194" s="2" t="s">
-        <v>1812</v>
+        <v>1821</v>
       </c>
       <c r="C1194" s="2" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="1195" customHeight="1" spans="1:4">
       <c r="A1195" s="2" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="B1195" s="2" t="s">
-        <v>1808</v>
+        <v>1813</v>
       </c>
       <c r="C1195" s="2" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="1196" customHeight="1" spans="1:4">
       <c r="A1196" s="2" t="s">
-        <v>1860</v>
-      </c>
-      <c r="B1196" s="2" t="s">
-        <v>1816</v>
+        <v>1861</v>
+      </c>
+      <c r="B1196" s="9" t="s">
+        <v>1862</v>
       </c>
       <c r="C1196" s="2" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="1197" customHeight="1" spans="1:4">
       <c r="A1197" s="2" t="s">
-        <v>1861</v>
+        <v>1863</v>
       </c>
       <c r="B1197" s="2" t="s">
-        <v>1862</v>
+        <v>1817</v>
       </c>
       <c r="C1197" s="2" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="1198" customHeight="1" spans="1:4">
-      <c r="A1198" s="27" t="s">
-        <v>1863</v>
+      <c r="A1198" s="2" t="s">
+        <v>1864</v>
       </c>
       <c r="B1198" s="2" t="s">
-        <v>1864</v>
+        <v>1813</v>
       </c>
       <c r="C1198" s="2" t="s">
-        <v>1865</v>
-      </c>
-      <c r="D1198" s="2" t="s">
-        <v>1866</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="1199" customHeight="1" spans="1:4">
       <c r="A1199" s="2" t="s">
+        <v>1865</v>
+      </c>
+      <c r="B1199" s="2" t="s">
+        <v>1821</v>
+      </c>
+      <c r="C1199" s="2" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="1200" customHeight="1" spans="1:4">
+      <c r="A1200" s="2" t="s">
+        <v>1866</v>
+      </c>
+      <c r="B1200" s="2" t="s">
         <v>1867</v>
       </c>
-      <c r="B1199" s="2" t="s">
+      <c r="C1200" s="2" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="1201" customHeight="1" spans="1:4">
+      <c r="A1201" s="27" t="s">
         <v>1868</v>
       </c>
-      <c r="C1199" s="2" t="s">
-        <v>1865</v>
+      <c r="B1201" s="2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C1201" s="2" t="s">
+        <v>1870</v>
+      </c>
+      <c r="D1201" s="2" t="s">
+        <v>1871</v>
+      </c>
+    </row>
+    <row r="1202" customHeight="1" spans="1:4">
+      <c r="A1202" s="2" t="s">
+        <v>1872</v>
+      </c>
+      <c r="B1202" s="2" t="s">
+        <v>1873</v>
+      </c>
+      <c r="C1202" s="2" t="s">
+        <v>1870</v>
       </c>
     </row>
   </sheetData>
